--- a/research/traditional_assets/database/data/greece/greece_healthcare_products.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_healthcare_products.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1256072652889646</v>
+        <v>0.1253660293053289</v>
       </c>
       <c r="C2">
-        <v>20.23458765178567</v>
+        <v>20.07221832216755</v>
       </c>
       <c r="D2">
-        <v>14.32458765178567</v>
+        <v>14.36801832216755</v>
       </c>
       <c r="E2">
-        <v>-10.7</v>
+        <v>-10.4942</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2058</v>
       </c>
       <c r="G2">
         <v>5.91</v>
@@ -1451,28 +1451,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01035174</v>
       </c>
       <c r="N2">
-        <v>2.146666666666667</v>
+        <v>2.136314926666667</v>
       </c>
       <c r="O2">
-        <v>0.4722666666666666</v>
+        <v>0.4699892838666667</v>
       </c>
       <c r="P2">
-        <v>1.6744</v>
+        <v>1.6663256428</v>
       </c>
       <c r="Q2">
-        <v>3.0744</v>
+        <v>3.0663256428</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1256072652889646</v>
+        <v>0.1262360498033625</v>
       </c>
       <c r="T2">
-        <v>1.040156204727314</v>
+        <v>1.048351374825166</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>207.3725447766913</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1253660293053289</v>
+        <v>0.1251247933216932</v>
       </c>
       <c r="C3">
-        <v>20.07221832216755</v>
+        <v>19.91011314805619</v>
       </c>
       <c r="D3">
-        <v>14.36801832216755</v>
+        <v>14.41171314805619</v>
       </c>
       <c r="E3">
-        <v>-10.4942</v>
+        <v>-10.2884</v>
       </c>
       <c r="F3">
-        <v>0.2058</v>
+        <v>0.4116</v>
       </c>
       <c r="G3">
         <v>5.91</v>
@@ -1533,28 +1533,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M3">
-        <v>0.01035174</v>
+        <v>0.02070348</v>
       </c>
       <c r="N3">
-        <v>2.136314926666667</v>
+        <v>2.125963186666667</v>
       </c>
       <c r="O3">
-        <v>0.4699892838666667</v>
+        <v>0.4677119010666667</v>
       </c>
       <c r="P3">
-        <v>1.6663256428</v>
+        <v>1.6582512856</v>
       </c>
       <c r="Q3">
-        <v>3.0663256428</v>
+        <v>3.0582512856</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1262360498033625</v>
+        <v>0.1268776666547889</v>
       </c>
       <c r="T3">
-        <v>1.048351374825166</v>
+        <v>1.056713793292361</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>207.3725447766913</v>
+        <v>103.6862723883457</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1251247933216932</v>
+        <v>0.1248835573380574</v>
       </c>
       <c r="C4">
-        <v>19.91011314805619</v>
+        <v>19.74827454678647</v>
       </c>
       <c r="D4">
-        <v>14.41171314805619</v>
+        <v>14.45567454678647</v>
       </c>
       <c r="E4">
-        <v>-10.2884</v>
+        <v>-10.0826</v>
       </c>
       <c r="F4">
-        <v>0.4116</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="G4">
         <v>5.91</v>
@@ -1615,28 +1615,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M4">
-        <v>0.02070348</v>
+        <v>0.03105521999999999</v>
       </c>
       <c r="N4">
-        <v>2.125963186666667</v>
+        <v>2.115611446666667</v>
       </c>
       <c r="O4">
-        <v>0.4677119010666667</v>
+        <v>0.4654345182666667</v>
       </c>
       <c r="P4">
-        <v>1.6582512856</v>
+        <v>1.6501769284</v>
       </c>
       <c r="Q4">
-        <v>3.0582512856</v>
+        <v>3.0501769284</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1268776666547889</v>
+        <v>0.1275325127196468</v>
       </c>
       <c r="T4">
-        <v>1.056713793292361</v>
+        <v>1.06524863275888</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>103.6862723883457</v>
+        <v>69.12418159223046</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1248835573380574</v>
+        <v>0.1246423213544217</v>
       </c>
       <c r="C5">
-        <v>19.74827454678647</v>
+        <v>19.58670496527878</v>
       </c>
       <c r="D5">
-        <v>14.45567454678647</v>
+        <v>14.49990496527878</v>
       </c>
       <c r="E5">
-        <v>-10.0826</v>
+        <v>-9.876799999999999</v>
       </c>
       <c r="F5">
-        <v>0.6173999999999999</v>
+        <v>0.8231999999999999</v>
       </c>
       <c r="G5">
         <v>5.91</v>
@@ -1697,28 +1697,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M5">
-        <v>0.03105521999999999</v>
+        <v>0.04140695999999999</v>
       </c>
       <c r="N5">
-        <v>2.115611446666667</v>
+        <v>2.105259706666667</v>
       </c>
       <c r="O5">
-        <v>0.4654345182666667</v>
+        <v>0.4631571354666667</v>
       </c>
       <c r="P5">
-        <v>1.6501769284</v>
+        <v>1.6421025712</v>
       </c>
       <c r="Q5">
-        <v>3.0501769284</v>
+        <v>3.0421025712</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1275325127196468</v>
+        <v>0.128201001410856</v>
       </c>
       <c r="T5">
-        <v>1.06524863275888</v>
+        <v>1.073961281380952</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>69.12418159223046</v>
+        <v>51.84313619417284</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1246423213544217</v>
+        <v>0.124401085370786</v>
       </c>
       <c r="C6">
-        <v>19.58670496527878</v>
+        <v>19.4254068804931</v>
       </c>
       <c r="D6">
-        <v>14.49990496527878</v>
+        <v>14.54440688049309</v>
       </c>
       <c r="E6">
-        <v>-9.876799999999999</v>
+        <v>-9.670999999999999</v>
       </c>
       <c r="F6">
-        <v>0.8231999999999999</v>
+        <v>1.029</v>
       </c>
       <c r="G6">
         <v>5.91</v>
@@ -1779,28 +1779,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M6">
-        <v>0.04140695999999999</v>
+        <v>0.05175869999999999</v>
       </c>
       <c r="N6">
-        <v>2.105259706666667</v>
+        <v>2.094907966666666</v>
       </c>
       <c r="O6">
-        <v>0.4631571354666667</v>
+        <v>0.4608797526666666</v>
       </c>
       <c r="P6">
-        <v>1.6421025712</v>
+        <v>1.634028214</v>
       </c>
       <c r="Q6">
-        <v>3.0421025712</v>
+        <v>3.034028214</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.128201001410856</v>
+        <v>0.1288835635481958</v>
       </c>
       <c r="T6">
-        <v>1.073961281380952</v>
+        <v>1.082857354184541</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>51.84313619417284</v>
+        <v>41.47450895533827</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.124401085370786</v>
+        <v>0.1241598493871503</v>
       </c>
       <c r="C7">
-        <v>19.4254068804931</v>
+        <v>19.2643827998913</v>
       </c>
       <c r="D7">
-        <v>14.54440688049309</v>
+        <v>14.5891827998913</v>
       </c>
       <c r="E7">
-        <v>-9.670999999999999</v>
+        <v>-9.465199999999999</v>
       </c>
       <c r="F7">
-        <v>1.029</v>
+        <v>1.2348</v>
       </c>
       <c r="G7">
         <v>5.91</v>
@@ -1861,28 +1861,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M7">
-        <v>0.05175869999999999</v>
+        <v>0.06211043999999999</v>
       </c>
       <c r="N7">
-        <v>2.094907966666666</v>
+        <v>2.084556226666666</v>
       </c>
       <c r="O7">
-        <v>0.4608797526666666</v>
+        <v>0.4586023698666666</v>
       </c>
       <c r="P7">
-        <v>1.634028214</v>
+        <v>1.6259538568</v>
       </c>
       <c r="Q7">
-        <v>3.034028214</v>
+        <v>3.0259538568</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1288835635481958</v>
+        <v>0.1295806482842024</v>
       </c>
       <c r="T7">
-        <v>1.082857354184541</v>
+        <v>1.091942705132887</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>41.47450895533827</v>
+        <v>34.56209079611522</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1241598493871503</v>
+        <v>0.1239186134035145</v>
       </c>
       <c r="C8">
-        <v>19.2643827998913</v>
+        <v>19.10363526190818</v>
       </c>
       <c r="D8">
-        <v>14.5891827998913</v>
+        <v>14.63423526190818</v>
       </c>
       <c r="E8">
-        <v>-9.465199999999999</v>
+        <v>-9.259399999999999</v>
       </c>
       <c r="F8">
-        <v>1.2348</v>
+        <v>1.4406</v>
       </c>
       <c r="G8">
         <v>5.91</v>
@@ -1943,28 +1943,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M8">
-        <v>0.06211043999999999</v>
+        <v>0.07246217999999997</v>
       </c>
       <c r="N8">
-        <v>2.084556226666666</v>
+        <v>2.074204486666666</v>
       </c>
       <c r="O8">
-        <v>0.4586023698666666</v>
+        <v>0.4563249870666666</v>
       </c>
       <c r="P8">
-        <v>1.6259538568</v>
+        <v>1.6178794996</v>
       </c>
       <c r="Q8">
-        <v>3.0259538568</v>
+        <v>3.0178794996</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1295806482842024</v>
+        <v>0.1302927240898006</v>
       </c>
       <c r="T8">
-        <v>1.091942705132887</v>
+        <v>1.101223439972595</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.56209079611522</v>
+        <v>29.62464925381305</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1239186134035146</v>
+        <v>0.1236773774198788</v>
       </c>
       <c r="C9">
-        <v>19.10363526190817</v>
+        <v>18.94316683643115</v>
       </c>
       <c r="D9">
-        <v>14.63423526190817</v>
+        <v>14.67956683643115</v>
       </c>
       <c r="E9">
-        <v>-9.259399999999999</v>
+        <v>-9.053599999999999</v>
       </c>
       <c r="F9">
-        <v>1.4406</v>
+        <v>1.6464</v>
       </c>
       <c r="G9">
         <v>5.91</v>
@@ -2025,28 +2025,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M9">
-        <v>0.07246218</v>
+        <v>0.08281391999999999</v>
       </c>
       <c r="N9">
-        <v>2.074204486666666</v>
+        <v>2.063852746666667</v>
       </c>
       <c r="O9">
-        <v>0.4563249870666666</v>
+        <v>0.4540476042666666</v>
       </c>
       <c r="P9">
-        <v>1.6178794996</v>
+        <v>1.6098051424</v>
       </c>
       <c r="Q9">
-        <v>3.0178794996</v>
+        <v>3.0098051424</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1302927240898006</v>
+        <v>0.1310202798042161</v>
       </c>
       <c r="T9">
-        <v>1.101223439972596</v>
+        <v>1.110705929917515</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.62464925381304</v>
+        <v>25.92156809708642</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1236773774198788</v>
+        <v>0.1234361414362431</v>
       </c>
       <c r="C10">
-        <v>18.94316683643115</v>
+        <v>18.7829801252889</v>
       </c>
       <c r="D10">
-        <v>14.67956683643115</v>
+        <v>14.7251801252889</v>
       </c>
       <c r="E10">
-        <v>-9.053599999999999</v>
+        <v>-8.847799999999999</v>
       </c>
       <c r="F10">
-        <v>1.6464</v>
+        <v>1.8522</v>
       </c>
       <c r="G10">
         <v>5.91</v>
@@ -2107,28 +2107,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M10">
-        <v>0.08281391999999999</v>
+        <v>0.09316565999999998</v>
       </c>
       <c r="N10">
-        <v>2.063852746666667</v>
+        <v>2.053501006666667</v>
       </c>
       <c r="O10">
-        <v>0.4540476042666666</v>
+        <v>0.4517702214666666</v>
       </c>
       <c r="P10">
-        <v>1.6098051424</v>
+        <v>1.6017307852</v>
       </c>
       <c r="Q10">
-        <v>3.0098051424</v>
+        <v>3.0017307852</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1310202798042161</v>
+        <v>0.1317638257541133</v>
       </c>
       <c r="T10">
-        <v>1.110705929917515</v>
+        <v>1.12039682623485</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.92156809708642</v>
+        <v>23.04139386407682</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1234361414362431</v>
+        <v>0.1231949054526074</v>
       </c>
       <c r="C11">
-        <v>18.7829801252889</v>
+        <v>18.62307776274919</v>
       </c>
       <c r="D11">
-        <v>14.7251801252889</v>
+        <v>14.77107776274919</v>
       </c>
       <c r="E11">
-        <v>-8.847799999999999</v>
+        <v>-8.641999999999999</v>
       </c>
       <c r="F11">
-        <v>1.8522</v>
+        <v>2.058</v>
       </c>
       <c r="G11">
         <v>5.91</v>
@@ -2189,28 +2189,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M11">
-        <v>0.09316565999999998</v>
+        <v>0.1035174</v>
       </c>
       <c r="N11">
-        <v>2.053501006666667</v>
+        <v>2.043149266666667</v>
       </c>
       <c r="O11">
-        <v>0.4517702214666666</v>
+        <v>0.4494928386666667</v>
       </c>
       <c r="P11">
-        <v>1.6017307852</v>
+        <v>1.593656428</v>
       </c>
       <c r="Q11">
-        <v>3.0017307852</v>
+        <v>2.993656428</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1317638257541133</v>
+        <v>0.1325238949473415</v>
       </c>
       <c r="T11">
-        <v>1.12039682623485</v>
+        <v>1.130303075803682</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.04139386407682</v>
+        <v>20.73725447766914</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1231949054526074</v>
+        <v>0.1229536694689717</v>
       </c>
       <c r="C12">
-        <v>18.62307776274919</v>
+        <v>18.46346241602599</v>
       </c>
       <c r="D12">
-        <v>14.77107776274919</v>
+        <v>14.81726241602598</v>
       </c>
       <c r="E12">
-        <v>-8.641999999999999</v>
+        <v>-8.436199999999999</v>
       </c>
       <c r="F12">
-        <v>2.058</v>
+        <v>2.2638</v>
       </c>
       <c r="G12">
         <v>5.91</v>
@@ -2271,28 +2271,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M12">
-        <v>0.1035174</v>
+        <v>0.11386914</v>
       </c>
       <c r="N12">
-        <v>2.043149266666667</v>
+        <v>2.032797526666667</v>
       </c>
       <c r="O12">
-        <v>0.4494928386666667</v>
+        <v>0.4472154558666667</v>
       </c>
       <c r="P12">
-        <v>1.593656428</v>
+        <v>1.5855820708</v>
       </c>
       <c r="Q12">
-        <v>2.993656428</v>
+        <v>2.9855820708</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1325238949473415</v>
+        <v>0.1333010443471592</v>
       </c>
       <c r="T12">
-        <v>1.130303075803682</v>
+        <v>1.140431937722375</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.73725447766914</v>
+        <v>18.85204952515376</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1229536694689717</v>
+        <v>0.122712433485336</v>
       </c>
       <c r="C13">
-        <v>18.46346241602599</v>
+        <v>18.30413678579612</v>
       </c>
       <c r="D13">
-        <v>14.81726241602598</v>
+        <v>14.86373678579612</v>
       </c>
       <c r="E13">
-        <v>-8.436199999999999</v>
+        <v>-8.230399999999999</v>
       </c>
       <c r="F13">
-        <v>2.2638</v>
+        <v>2.4696</v>
       </c>
       <c r="G13">
         <v>5.91</v>
@@ -2353,28 +2353,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M13">
-        <v>0.11386914</v>
+        <v>0.12422088</v>
       </c>
       <c r="N13">
-        <v>2.032797526666667</v>
+        <v>2.022445786666666</v>
       </c>
       <c r="O13">
-        <v>0.4472154558666667</v>
+        <v>0.4449380730666666</v>
       </c>
       <c r="P13">
-        <v>1.5855820708</v>
+        <v>1.5775077136</v>
       </c>
       <c r="Q13">
-        <v>2.9855820708</v>
+        <v>2.9775077136</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1333010443471592</v>
+        <v>0.1340958562333363</v>
       </c>
       <c r="T13">
-        <v>1.140431937722375</v>
+        <v>1.15079100104831</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.85204952515376</v>
+        <v>17.28104539805761</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.122712433485336</v>
+        <v>0.1224711975017002</v>
       </c>
       <c r="C14">
-        <v>18.30413678579612</v>
+        <v>18.14510360672577</v>
       </c>
       <c r="D14">
-        <v>14.86373678579612</v>
+        <v>14.91050360672577</v>
       </c>
       <c r="E14">
-        <v>-8.230399999999999</v>
+        <v>-8.0246</v>
       </c>
       <c r="F14">
-        <v>2.4696</v>
+        <v>2.6754</v>
       </c>
       <c r="G14">
         <v>5.91</v>
@@ -2435,28 +2435,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M14">
-        <v>0.12422088</v>
+        <v>0.13457262</v>
       </c>
       <c r="N14">
-        <v>2.022445786666666</v>
+        <v>2.012094046666666</v>
       </c>
       <c r="O14">
-        <v>0.4449380730666666</v>
+        <v>0.4426606902666666</v>
       </c>
       <c r="P14">
-        <v>1.5775077136</v>
+        <v>1.5694333564</v>
       </c>
       <c r="Q14">
-        <v>2.9775077136</v>
+        <v>2.9694333564</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1340958562333363</v>
+        <v>0.1349089396571267</v>
       </c>
       <c r="T14">
-        <v>1.15079100104831</v>
+        <v>1.161388203761049</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.28104539805761</v>
+        <v>15.95173421359164</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1224711975017002</v>
+        <v>0.1222299615180645</v>
       </c>
       <c r="C15">
-        <v>18.14510360672577</v>
+        <v>17.98636564800683</v>
       </c>
       <c r="D15">
-        <v>14.91050360672577</v>
+        <v>14.95756564800683</v>
       </c>
       <c r="E15">
-        <v>-8.0246</v>
+        <v>-7.8188</v>
       </c>
       <c r="F15">
-        <v>2.6754</v>
+        <v>2.8812</v>
       </c>
       <c r="G15">
         <v>5.91</v>
@@ -2517,28 +2517,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M15">
-        <v>0.13457262</v>
+        <v>0.14492436</v>
       </c>
       <c r="N15">
-        <v>2.012094046666666</v>
+        <v>2.001742306666666</v>
       </c>
       <c r="O15">
-        <v>0.4426606902666666</v>
+        <v>0.4403833074666666</v>
       </c>
       <c r="P15">
-        <v>1.5694333564</v>
+        <v>1.5613589992</v>
       </c>
       <c r="Q15">
-        <v>2.9694333564</v>
+        <v>2.9613589992</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1349089396571267</v>
+        <v>0.1357409319977494</v>
       </c>
       <c r="T15">
-        <v>1.161388203761049</v>
+        <v>1.172231853048504</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.95173421359164</v>
+        <v>14.81232462690652</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1222299615180645</v>
+        <v>0.1219887255344288</v>
       </c>
       <c r="C16">
-        <v>17.98636564800683</v>
+        <v>17.82792571390348</v>
       </c>
       <c r="D16">
-        <v>14.95756564800683</v>
+        <v>15.00492571390348</v>
       </c>
       <c r="E16">
-        <v>-7.8188</v>
+        <v>-7.613</v>
       </c>
       <c r="F16">
-        <v>2.8812</v>
+        <v>3.087</v>
       </c>
       <c r="G16">
         <v>5.91</v>
@@ -2599,28 +2599,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M16">
-        <v>0.14492436</v>
+        <v>0.1552761</v>
       </c>
       <c r="N16">
-        <v>2.001742306666666</v>
+        <v>1.991390566666666</v>
       </c>
       <c r="O16">
-        <v>0.4403833074666666</v>
+        <v>0.4381059246666666</v>
       </c>
       <c r="P16">
-        <v>1.5613589992</v>
+        <v>1.553284642</v>
       </c>
       <c r="Q16">
-        <v>2.9613589992</v>
+        <v>2.953284642</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1357409319977494</v>
+        <v>0.1365925006287397</v>
       </c>
       <c r="T16">
-        <v>1.172231853048504</v>
+        <v>1.183330647025074</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.81232462690652</v>
+        <v>13.82483631844609</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1219887255344288</v>
+        <v>0.121747489550793</v>
       </c>
       <c r="C17">
-        <v>17.82792571390348</v>
+        <v>17.66978664430927</v>
       </c>
       <c r="D17">
-        <v>15.00492571390348</v>
+        <v>15.05258664430927</v>
       </c>
       <c r="E17">
-        <v>-7.613</v>
+        <v>-7.4072</v>
       </c>
       <c r="F17">
-        <v>3.087</v>
+        <v>3.2928</v>
       </c>
       <c r="G17">
         <v>5.91</v>
@@ -2681,28 +2681,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M17">
-        <v>0.1552761</v>
+        <v>0.16562784</v>
       </c>
       <c r="N17">
-        <v>1.991390566666666</v>
+        <v>1.981038826666667</v>
       </c>
       <c r="O17">
-        <v>0.4381059246666666</v>
+        <v>0.4358285418666666</v>
       </c>
       <c r="P17">
-        <v>1.553284642</v>
+        <v>1.5452102848</v>
       </c>
       <c r="Q17">
-        <v>2.953284642</v>
+        <v>2.9452102848</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1365925006287397</v>
+        <v>0.1374643447033251</v>
       </c>
       <c r="T17">
-        <v>1.183330647025074</v>
+        <v>1.194693698001087</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.82483631844609</v>
+        <v>12.96078404854321</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.121747489550793</v>
+        <v>0.1217051535671573</v>
       </c>
       <c r="C18">
-        <v>17.66978664430927</v>
+        <v>17.47238220155275</v>
       </c>
       <c r="D18">
-        <v>15.05258664430927</v>
+        <v>15.06098220155275</v>
       </c>
       <c r="E18">
-        <v>-7.4072</v>
+        <v>-7.2014</v>
       </c>
       <c r="F18">
-        <v>3.2928</v>
+        <v>3.4986</v>
       </c>
       <c r="G18">
         <v>5.91</v>
@@ -2763,45 +2763,45 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M18">
-        <v>0.16562784</v>
+        <v>0.18122748</v>
       </c>
       <c r="N18">
-        <v>1.981038826666667</v>
+        <v>1.965439186666667</v>
       </c>
       <c r="O18">
-        <v>0.4358285418666666</v>
+        <v>0.4323966210666667</v>
       </c>
       <c r="P18">
-        <v>1.5452102848</v>
+        <v>1.5330425656</v>
       </c>
       <c r="Q18">
-        <v>2.9452102848</v>
+        <v>2.9330425656</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1374643447033251</v>
+        <v>0.1383571970688643</v>
       </c>
       <c r="T18">
-        <v>1.194693698001087</v>
+        <v>1.206330557434353</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>12.96078404854321</v>
+        <v>11.84514990037199</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1217051535671573</v>
+        <v>0.1214756175835216</v>
       </c>
       <c r="C19">
-        <v>17.47238220155275</v>
+        <v>17.3122645160755</v>
       </c>
       <c r="D19">
-        <v>15.06098220155275</v>
+        <v>15.1066645160755</v>
       </c>
       <c r="E19">
-        <v>-7.2014</v>
+        <v>-6.9956</v>
       </c>
       <c r="F19">
-        <v>3.4986</v>
+        <v>3.7044</v>
       </c>
       <c r="G19">
         <v>5.91</v>
@@ -2845,28 +2845,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M19">
-        <v>0.18122748</v>
+        <v>0.19188792</v>
       </c>
       <c r="N19">
-        <v>1.965439186666667</v>
+        <v>1.954778746666666</v>
       </c>
       <c r="O19">
-        <v>0.4323966210666667</v>
+        <v>0.4300513242666666</v>
       </c>
       <c r="P19">
-        <v>1.5330425656</v>
+        <v>1.5247274224</v>
       </c>
       <c r="Q19">
-        <v>2.9330425656</v>
+        <v>2.9247274224</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1383571970688643</v>
+        <v>0.1392718263213678</v>
       </c>
       <c r="T19">
-        <v>1.206330557434353</v>
+        <v>1.218251242707455</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.84514990037199</v>
+        <v>11.18708601701799</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1214756175835216</v>
+        <v>0.1212460815998859</v>
       </c>
       <c r="C20">
-        <v>17.3122645160755</v>
+        <v>17.15242479692271</v>
       </c>
       <c r="D20">
-        <v>15.1066645160755</v>
+        <v>15.15262479692271</v>
       </c>
       <c r="E20">
-        <v>-6.9956</v>
+        <v>-6.7898</v>
       </c>
       <c r="F20">
-        <v>3.7044</v>
+        <v>3.9102</v>
       </c>
       <c r="G20">
         <v>5.91</v>
@@ -2927,28 +2927,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M20">
-        <v>0.19188792</v>
+        <v>0.20254836</v>
       </c>
       <c r="N20">
-        <v>1.954778746666666</v>
+        <v>1.944118306666667</v>
       </c>
       <c r="O20">
-        <v>0.4300513242666666</v>
+        <v>0.4277060274666666</v>
       </c>
       <c r="P20">
-        <v>1.5247274224</v>
+        <v>1.5164122792</v>
       </c>
       <c r="Q20">
-        <v>2.9247274224</v>
+        <v>2.9164122792</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1392718263213678</v>
+        <v>0.1402090390122048</v>
       </c>
       <c r="T20">
-        <v>1.218251242707454</v>
+        <v>1.230466265888534</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.18708601701799</v>
+        <v>10.59829201612231</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1212460815998859</v>
+        <v>0.1210165456162502</v>
       </c>
       <c r="C21">
-        <v>17.15242479692271</v>
+        <v>16.99286558887784</v>
       </c>
       <c r="D21">
-        <v>15.15262479692271</v>
+        <v>15.19886558887784</v>
       </c>
       <c r="E21">
-        <v>-6.7898</v>
+        <v>-6.584</v>
       </c>
       <c r="F21">
-        <v>3.9102</v>
+        <v>4.116</v>
       </c>
       <c r="G21">
         <v>5.91</v>
@@ -3009,28 +3009,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M21">
-        <v>0.20254836</v>
+        <v>0.2132088</v>
       </c>
       <c r="N21">
-        <v>1.944118306666667</v>
+        <v>1.933457866666667</v>
       </c>
       <c r="O21">
-        <v>0.4277060274666666</v>
+        <v>0.4253607306666667</v>
       </c>
       <c r="P21">
-        <v>1.5164122792</v>
+        <v>1.508097136</v>
       </c>
       <c r="Q21">
-        <v>2.9164122792</v>
+        <v>2.908097136</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1402090390122048</v>
+        <v>0.1411696820203127</v>
       </c>
       <c r="T21">
-        <v>1.230466265888534</v>
+        <v>1.242986664649141</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.59829201612231</v>
+        <v>10.06837741531619</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1210165456162502</v>
+        <v>0.1210654696326145</v>
       </c>
       <c r="C22">
-        <v>16.99286558887784</v>
+        <v>16.77718603119463</v>
       </c>
       <c r="D22">
-        <v>15.19886558887784</v>
+        <v>15.18898603119464</v>
       </c>
       <c r="E22">
-        <v>-6.584</v>
+        <v>-6.3782</v>
       </c>
       <c r="F22">
-        <v>4.116</v>
+        <v>4.3218</v>
       </c>
       <c r="G22">
         <v>5.91</v>
@@ -3091,45 +3091,45 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M22">
-        <v>0.2132088</v>
+        <v>0.2312163</v>
       </c>
       <c r="N22">
-        <v>1.933457866666667</v>
+        <v>1.915450366666666</v>
       </c>
       <c r="O22">
-        <v>0.4253607306666667</v>
+        <v>0.4213990806666666</v>
       </c>
       <c r="P22">
-        <v>1.508097136</v>
+        <v>1.494051286</v>
       </c>
       <c r="Q22">
-        <v>2.908097136</v>
+        <v>2.894051286</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1411696820203127</v>
+        <v>0.1421546451045753</v>
       </c>
       <c r="T22">
-        <v>1.242986664649141</v>
+        <v>1.255824035530269</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>10.06837741531619</v>
+        <v>9.284235872067265</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1210654696326144</v>
+        <v>0.1208491936489787</v>
       </c>
       <c r="C23">
-        <v>16.77718603119464</v>
+        <v>16.61515749274679</v>
       </c>
       <c r="D23">
-        <v>15.18898603119464</v>
+        <v>15.23275749274679</v>
       </c>
       <c r="E23">
-        <v>-6.3782</v>
+        <v>-6.1724</v>
       </c>
       <c r="F23">
-        <v>4.3218</v>
+        <v>4.5276</v>
       </c>
       <c r="G23">
         <v>5.91</v>
@@ -3173,28 +3173,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M23">
-        <v>0.2312163</v>
+        <v>0.2422266</v>
       </c>
       <c r="N23">
-        <v>1.915450366666666</v>
+        <v>1.904440066666667</v>
       </c>
       <c r="O23">
-        <v>0.4213990806666666</v>
+        <v>0.4189768146666666</v>
       </c>
       <c r="P23">
-        <v>1.494051286</v>
+        <v>1.485463252</v>
       </c>
       <c r="Q23">
-        <v>2.894051286</v>
+        <v>2.885463252</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1421546451045752</v>
+        <v>0.1431648636525368</v>
       </c>
       <c r="T23">
-        <v>1.255824035530269</v>
+        <v>1.268990569767323</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.284235872067265</v>
+        <v>8.862225150609664</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1208491936489787</v>
+        <v>0.120632917665343</v>
       </c>
       <c r="C24">
-        <v>16.61515749274679</v>
+        <v>16.45338196370168</v>
       </c>
       <c r="D24">
-        <v>15.23275749274679</v>
+        <v>15.27678196370168</v>
       </c>
       <c r="E24">
-        <v>-6.1724</v>
+        <v>-5.9666</v>
       </c>
       <c r="F24">
-        <v>4.5276</v>
+        <v>4.7334</v>
       </c>
       <c r="G24">
         <v>5.91</v>
@@ -3255,28 +3255,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M24">
-        <v>0.2422266</v>
+        <v>0.2532369</v>
       </c>
       <c r="N24">
-        <v>1.904440066666667</v>
+        <v>1.893429766666666</v>
       </c>
       <c r="O24">
-        <v>0.4189768146666666</v>
+        <v>0.4165545486666666</v>
       </c>
       <c r="P24">
-        <v>1.485463252</v>
+        <v>1.476875218</v>
       </c>
       <c r="Q24">
-        <v>2.885463252</v>
+        <v>2.876875218</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1431648636525368</v>
+        <v>0.1442013216433026</v>
       </c>
       <c r="T24">
-        <v>1.268990569767323</v>
+        <v>1.282499091906639</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.862225150609664</v>
+        <v>8.476911013626633</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.120632917665343</v>
+        <v>0.1204166416817073</v>
       </c>
       <c r="C25">
-        <v>16.45338196370168</v>
+        <v>16.29186164409901</v>
       </c>
       <c r="D25">
-        <v>15.27678196370168</v>
+        <v>15.32106164409901</v>
       </c>
       <c r="E25">
-        <v>-5.9666</v>
+        <v>-5.7608</v>
       </c>
       <c r="F25">
-        <v>4.7334</v>
+        <v>4.9392</v>
       </c>
       <c r="G25">
         <v>5.91</v>
@@ -3337,28 +3337,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M25">
-        <v>0.2532369</v>
+        <v>0.2642472</v>
       </c>
       <c r="N25">
-        <v>1.893429766666666</v>
+        <v>1.882419466666666</v>
       </c>
       <c r="O25">
-        <v>0.4165545486666666</v>
+        <v>0.4141322826666666</v>
       </c>
       <c r="P25">
-        <v>1.476875218</v>
+        <v>1.468287184</v>
       </c>
       <c r="Q25">
-        <v>2.876875218</v>
+        <v>2.868287184</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1442013216433026</v>
+        <v>0.1452650548443517</v>
       </c>
       <c r="T25">
-        <v>1.282499091906639</v>
+        <v>1.296363101470674</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.476911013626633</v>
+        <v>8.123706388058858</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1204166416817073</v>
+        <v>0.1202003656980715</v>
       </c>
       <c r="C26">
-        <v>16.29186164409901</v>
+        <v>16.13059875955982</v>
       </c>
       <c r="D26">
-        <v>15.32106164409901</v>
+        <v>15.36559875955982</v>
       </c>
       <c r="E26">
-        <v>-5.7608</v>
+        <v>-5.555</v>
       </c>
       <c r="F26">
-        <v>4.9392</v>
+        <v>5.145</v>
       </c>
       <c r="G26">
         <v>5.91</v>
@@ -3419,28 +3419,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M26">
-        <v>0.2642472</v>
+        <v>0.2752575</v>
       </c>
       <c r="N26">
-        <v>1.882419466666666</v>
+        <v>1.871409166666667</v>
       </c>
       <c r="O26">
-        <v>0.4141322826666666</v>
+        <v>0.4117100166666666</v>
       </c>
       <c r="P26">
-        <v>1.468287184</v>
+        <v>1.45969915</v>
       </c>
       <c r="Q26">
-        <v>2.868287184</v>
+        <v>2.85969915</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1452650548443517</v>
+        <v>0.1463571542640954</v>
       </c>
       <c r="T26">
-        <v>1.296363101470674</v>
+        <v>1.310596817956416</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.123706388058858</v>
+        <v>7.798758132536504</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1202003656980715</v>
+        <v>0.1201463297144358</v>
       </c>
       <c r="C27">
-        <v>16.13059875955982</v>
+        <v>15.9359666981294</v>
       </c>
       <c r="D27">
-        <v>15.36559875955982</v>
+        <v>15.3767666981294</v>
       </c>
       <c r="E27">
-        <v>-5.555</v>
+        <v>-5.3492</v>
       </c>
       <c r="F27">
-        <v>5.145</v>
+        <v>5.3508</v>
       </c>
       <c r="G27">
         <v>5.91</v>
@@ -3501,45 +3501,45 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M27">
-        <v>0.2752575</v>
+        <v>0.29054844</v>
       </c>
       <c r="N27">
-        <v>1.871409166666667</v>
+        <v>1.856118226666666</v>
       </c>
       <c r="O27">
-        <v>0.4117100166666666</v>
+        <v>0.4083460098666666</v>
       </c>
       <c r="P27">
-        <v>1.45969915</v>
+        <v>1.4477722168</v>
       </c>
       <c r="Q27">
-        <v>2.85969915</v>
+        <v>2.8477722168</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1463571542640954</v>
+        <v>0.1474787698843728</v>
       </c>
       <c r="T27">
-        <v>1.310596817956416</v>
+        <v>1.325215229482313</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.798758132536504</v>
+        <v>7.388326251783237</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1201463297144358</v>
+        <v>0.1199362937308001</v>
       </c>
       <c r="C28">
-        <v>15.9359666981294</v>
+        <v>15.77373070916974</v>
       </c>
       <c r="D28">
-        <v>15.3767666981294</v>
+        <v>15.42033070916974</v>
       </c>
       <c r="E28">
-        <v>-5.3492</v>
+        <v>-5.1434</v>
       </c>
       <c r="F28">
-        <v>5.3508</v>
+        <v>5.5566</v>
       </c>
       <c r="G28">
         <v>5.91</v>
@@ -3583,28 +3583,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M28">
-        <v>0.29054844</v>
+        <v>0.30172338</v>
       </c>
       <c r="N28">
-        <v>1.856118226666666</v>
+        <v>1.844943286666667</v>
       </c>
       <c r="O28">
-        <v>0.4083460098666666</v>
+        <v>0.4058875230666666</v>
       </c>
       <c r="P28">
-        <v>1.4477722168</v>
+        <v>1.4390557636</v>
       </c>
       <c r="Q28">
-        <v>2.8477722168</v>
+        <v>2.8390557636</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1474787698843728</v>
+        <v>0.1486311146997262</v>
       </c>
       <c r="T28">
-        <v>1.325215229482313</v>
+        <v>1.340234145433578</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.388326251783237</v>
+        <v>7.114684538754228</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1199362937308001</v>
+        <v>0.1197262577471644</v>
       </c>
       <c r="C29">
-        <v>15.77373070916974</v>
+        <v>15.61174226445726</v>
       </c>
       <c r="D29">
-        <v>15.42033070916974</v>
+        <v>15.46414226445725</v>
       </c>
       <c r="E29">
-        <v>-5.1434</v>
+        <v>-4.937599999999999</v>
       </c>
       <c r="F29">
-        <v>5.5566</v>
+        <v>5.7624</v>
       </c>
       <c r="G29">
         <v>5.91</v>
@@ -3665,28 +3665,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M29">
-        <v>0.30172338</v>
+        <v>0.31289832</v>
       </c>
       <c r="N29">
-        <v>1.844943286666667</v>
+        <v>1.833768346666667</v>
       </c>
       <c r="O29">
-        <v>0.4058875230666666</v>
+        <v>0.4034290362666667</v>
       </c>
       <c r="P29">
-        <v>1.4390557636</v>
+        <v>1.4303393104</v>
       </c>
       <c r="Q29">
-        <v>2.8390557636</v>
+        <v>2.8303393104</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1486311146997262</v>
+        <v>0.1498154690932839</v>
       </c>
       <c r="T29">
-        <v>1.340234145433578</v>
+        <v>1.3556702534946</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.114684538754228</v>
+        <v>6.860588662370148</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1197262577471644</v>
+        <v>0.1195162217635287</v>
       </c>
       <c r="C30">
-        <v>15.61174226445726</v>
+        <v>15.45000347993866</v>
       </c>
       <c r="D30">
-        <v>15.46414226445725</v>
+        <v>15.50820347993866</v>
       </c>
       <c r="E30">
-        <v>-4.937599999999999</v>
+        <v>-4.731799999999999</v>
       </c>
       <c r="F30">
-        <v>5.7624</v>
+        <v>5.9682</v>
       </c>
       <c r="G30">
         <v>5.91</v>
@@ -3747,28 +3747,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M30">
-        <v>0.31289832</v>
+        <v>0.32407326</v>
       </c>
       <c r="N30">
-        <v>1.833768346666667</v>
+        <v>1.822593406666666</v>
       </c>
       <c r="O30">
-        <v>0.4034290362666667</v>
+        <v>0.4009705494666666</v>
       </c>
       <c r="P30">
-        <v>1.4303393104</v>
+        <v>1.4216228572</v>
       </c>
       <c r="Q30">
-        <v>2.8303393104</v>
+        <v>2.8216228572</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1498154690932839</v>
+        <v>0.1510331855824348</v>
       </c>
       <c r="T30">
-        <v>1.3556702534946</v>
+        <v>1.371541181501002</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.860588662370148</v>
+        <v>6.624016639529797</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1195162217635287</v>
+        <v>0.119306185779893</v>
       </c>
       <c r="C31">
-        <v>15.45000347993866</v>
+        <v>15.28851649574505</v>
       </c>
       <c r="D31">
-        <v>15.50820347993866</v>
+        <v>15.55251649574505</v>
       </c>
       <c r="E31">
-        <v>-4.7318</v>
+        <v>-4.526</v>
       </c>
       <c r="F31">
-        <v>5.9682</v>
+        <v>6.173999999999999</v>
       </c>
       <c r="G31">
         <v>5.91</v>
@@ -3829,28 +3829,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M31">
-        <v>0.32407326</v>
+        <v>0.3352482</v>
       </c>
       <c r="N31">
-        <v>1.822593406666666</v>
+        <v>1.811418466666666</v>
       </c>
       <c r="O31">
-        <v>0.4009705494666666</v>
+        <v>0.3985120626666666</v>
       </c>
       <c r="P31">
-        <v>1.4216228572</v>
+        <v>1.412906404</v>
       </c>
       <c r="Q31">
-        <v>2.8216228572</v>
+        <v>2.812906404</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1510331855824348</v>
+        <v>0.1522856939712756</v>
       </c>
       <c r="T31">
-        <v>1.371541181501002</v>
+        <v>1.387865564593302</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.624016639529798</v>
+        <v>6.403216084878805</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.119306185779893</v>
+        <v>0.1190961497962572</v>
       </c>
       <c r="C32">
-        <v>15.28851649574505</v>
+        <v>15.12728347653838</v>
       </c>
       <c r="D32">
-        <v>15.55251649574505</v>
+        <v>15.59708347653838</v>
       </c>
       <c r="E32">
-        <v>-4.526</v>
+        <v>-4.3202</v>
       </c>
       <c r="F32">
-        <v>6.173999999999999</v>
+        <v>6.379799999999999</v>
       </c>
       <c r="G32">
         <v>5.91</v>
@@ -3911,28 +3911,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M32">
-        <v>0.3352482</v>
+        <v>0.34642314</v>
       </c>
       <c r="N32">
-        <v>1.811418466666666</v>
+        <v>1.800243526666667</v>
       </c>
       <c r="O32">
-        <v>0.3985120626666666</v>
+        <v>0.3960535758666666</v>
       </c>
       <c r="P32">
-        <v>1.412906404</v>
+        <v>1.4041899508</v>
       </c>
       <c r="Q32">
-        <v>2.812906404</v>
+        <v>2.8041899508</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1522856939712756</v>
+        <v>0.1535745069510974</v>
       </c>
       <c r="T32">
-        <v>1.387865564593302</v>
+        <v>1.404663118210017</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.403216084878805</v>
+        <v>6.19666072730207</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1190961497962572</v>
+        <v>0.1191357138126215</v>
       </c>
       <c r="C33">
-        <v>15.12728347653838</v>
+        <v>14.91306897787437</v>
       </c>
       <c r="D33">
-        <v>15.59708347653838</v>
+        <v>15.58866897787436</v>
       </c>
       <c r="E33">
-        <v>-4.3202</v>
+        <v>-4.1144</v>
       </c>
       <c r="F33">
-        <v>6.379799999999999</v>
+        <v>6.585599999999999</v>
       </c>
       <c r="G33">
         <v>5.91</v>
@@ -3993,45 +3993,45 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M33">
-        <v>0.34642314</v>
+        <v>0.36418368</v>
       </c>
       <c r="N33">
-        <v>1.800243526666667</v>
+        <v>1.782482986666666</v>
       </c>
       <c r="O33">
-        <v>0.3960535758666666</v>
+        <v>0.3921462570666666</v>
       </c>
       <c r="P33">
-        <v>1.4041899508</v>
+        <v>1.3903367296</v>
       </c>
       <c r="Q33">
-        <v>2.8041899508</v>
+        <v>2.7903367296</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1535745069510974</v>
+        <v>0.1549012261950316</v>
       </c>
       <c r="T33">
-        <v>1.404663118210017</v>
+        <v>1.42195471752134</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.22</v>
       </c>
       <c r="W33">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.19666072730207</v>
+        <v>5.894461461498402</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1191357138126215</v>
+        <v>0.1189334778289858</v>
       </c>
       <c r="C34">
-        <v>14.91306897787437</v>
+        <v>14.75037631938059</v>
       </c>
       <c r="D34">
-        <v>15.58866897787436</v>
+        <v>15.63177631938059</v>
       </c>
       <c r="E34">
-        <v>-4.1144</v>
+        <v>-3.9086</v>
       </c>
       <c r="F34">
-        <v>6.585599999999999</v>
+        <v>6.791399999999999</v>
       </c>
       <c r="G34">
         <v>5.91</v>
@@ -4075,28 +4075,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M34">
-        <v>0.36418368</v>
+        <v>0.37556442</v>
       </c>
       <c r="N34">
-        <v>1.782482986666666</v>
+        <v>1.771102246666667</v>
       </c>
       <c r="O34">
-        <v>0.3921462570666666</v>
+        <v>0.3896424942666666</v>
       </c>
       <c r="P34">
-        <v>1.3903367296</v>
+        <v>1.3814597524</v>
       </c>
       <c r="Q34">
-        <v>2.7903367296</v>
+        <v>2.7814597524</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1549012261950316</v>
+        <v>0.1562675489984862</v>
       </c>
       <c r="T34">
-        <v>1.42195471752134</v>
+        <v>1.439762483976285</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.894461461498402</v>
+        <v>5.715841417210573</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1189334778289858</v>
+        <v>0.1187312418453501</v>
       </c>
       <c r="C35">
-        <v>14.75037631938059</v>
+        <v>14.58792273142479</v>
       </c>
       <c r="D35">
-        <v>15.63177631938059</v>
+        <v>15.67512273142479</v>
       </c>
       <c r="E35">
-        <v>-3.9086</v>
+        <v>-3.702799999999999</v>
       </c>
       <c r="F35">
-        <v>6.791399999999999</v>
+        <v>6.9972</v>
       </c>
       <c r="G35">
         <v>5.91</v>
@@ -4157,28 +4157,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M35">
-        <v>0.37556442</v>
+        <v>0.38694516</v>
       </c>
       <c r="N35">
-        <v>1.771102246666667</v>
+        <v>1.759721506666666</v>
       </c>
       <c r="O35">
-        <v>0.3896424942666666</v>
+        <v>0.3871387314666666</v>
       </c>
       <c r="P35">
-        <v>1.3814597524</v>
+        <v>1.3725827752</v>
       </c>
       <c r="Q35">
-        <v>2.7814597524</v>
+        <v>2.7725827752</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1562675489984862</v>
+        <v>0.1576752755232577</v>
       </c>
       <c r="T35">
-        <v>1.439762483976285</v>
+        <v>1.458109879717744</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.715841417210573</v>
+        <v>5.547728434351438</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1187312418453501</v>
+        <v>0.1185290058617143</v>
       </c>
       <c r="C36">
-        <v>14.58792273142479</v>
+        <v>14.42571020834187</v>
       </c>
       <c r="D36">
-        <v>15.67512273142479</v>
+        <v>15.71871020834187</v>
       </c>
       <c r="E36">
-        <v>-3.702799999999999</v>
+        <v>-3.496999999999999</v>
       </c>
       <c r="F36">
-        <v>6.9972</v>
+        <v>7.203</v>
       </c>
       <c r="G36">
         <v>5.91</v>
@@ -4239,28 +4239,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M36">
-        <v>0.38694516</v>
+        <v>0.3983259</v>
       </c>
       <c r="N36">
-        <v>1.759721506666666</v>
+        <v>1.748340766666666</v>
       </c>
       <c r="O36">
-        <v>0.3871387314666666</v>
+        <v>0.3846349686666666</v>
       </c>
       <c r="P36">
-        <v>1.3725827752</v>
+        <v>1.363705798</v>
       </c>
       <c r="Q36">
-        <v>2.7725827752</v>
+        <v>2.763705798</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1576752755232577</v>
+        <v>0.1591263167103298</v>
       </c>
       <c r="T36">
-        <v>1.458109879717744</v>
+        <v>1.477021810712786</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.547728434351438</v>
+        <v>5.389221907655682</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1185290058617143</v>
+        <v>0.1183267698780786</v>
       </c>
       <c r="C37">
-        <v>14.42571020834187</v>
+        <v>14.26374076671105</v>
       </c>
       <c r="D37">
-        <v>15.71871020834187</v>
+        <v>15.76254076671105</v>
       </c>
       <c r="E37">
-        <v>-3.496999999999999</v>
+        <v>-3.291199999999999</v>
       </c>
       <c r="F37">
-        <v>7.203</v>
+        <v>7.4088</v>
       </c>
       <c r="G37">
         <v>5.91</v>
@@ -4321,28 +4321,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M37">
-        <v>0.3983259</v>
+        <v>0.40970664</v>
       </c>
       <c r="N37">
-        <v>1.748340766666666</v>
+        <v>1.736960026666666</v>
       </c>
       <c r="O37">
-        <v>0.3846349686666666</v>
+        <v>0.3821312058666667</v>
       </c>
       <c r="P37">
-        <v>1.363705798</v>
+        <v>1.3548288208</v>
       </c>
       <c r="Q37">
-        <v>2.763705798</v>
+        <v>2.7548288208</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1591263167103298</v>
+        <v>0.1606227029344978</v>
       </c>
       <c r="T37">
-        <v>1.477021810712786</v>
+        <v>1.496524739551424</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.389221907655682</v>
+        <v>5.239521299109691</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1183267698780786</v>
+        <v>0.1181245338944429</v>
       </c>
       <c r="C38">
-        <v>14.26374076671105</v>
+        <v>14.10201644566677</v>
       </c>
       <c r="D38">
-        <v>15.76254076671105</v>
+        <v>15.80661644566677</v>
       </c>
       <c r="E38">
-        <v>-3.2912</v>
+        <v>-3.0854</v>
       </c>
       <c r="F38">
-        <v>7.408799999999999</v>
+        <v>7.614599999999999</v>
       </c>
       <c r="G38">
         <v>5.91</v>
@@ -4403,28 +4403,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M38">
-        <v>0.40970664</v>
+        <v>0.42108738</v>
       </c>
       <c r="N38">
-        <v>1.736960026666666</v>
+        <v>1.725579286666667</v>
       </c>
       <c r="O38">
-        <v>0.3821312058666667</v>
+        <v>0.3796274430666667</v>
       </c>
       <c r="P38">
-        <v>1.3548288208</v>
+        <v>1.3459518436</v>
       </c>
       <c r="Q38">
-        <v>2.7548288208</v>
+        <v>2.7459518436</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1606227029344978</v>
+        <v>0.1621665934832427</v>
       </c>
       <c r="T38">
-        <v>1.496524739551423</v>
+        <v>1.516646808988113</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.239521299109692</v>
+        <v>5.09791261534997</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1181245338944429</v>
+        <v>0.1179222979108072</v>
       </c>
       <c r="C39">
-        <v>14.10201644566677</v>
+        <v>13.94053930721502</v>
       </c>
       <c r="D39">
-        <v>15.80661644566677</v>
+        <v>15.85093930721502</v>
       </c>
       <c r="E39">
-        <v>-3.0854</v>
+        <v>-2.8796</v>
       </c>
       <c r="F39">
-        <v>7.614599999999999</v>
+        <v>7.820399999999999</v>
       </c>
       <c r="G39">
         <v>5.91</v>
@@ -4485,28 +4485,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M39">
-        <v>0.42108738</v>
+        <v>0.43246812</v>
       </c>
       <c r="N39">
-        <v>1.725579286666667</v>
+        <v>1.714198546666666</v>
       </c>
       <c r="O39">
-        <v>0.3796274430666667</v>
+        <v>0.3771236802666666</v>
       </c>
       <c r="P39">
-        <v>1.3459518436</v>
+        <v>1.3370748664</v>
       </c>
       <c r="Q39">
-        <v>2.7459518436</v>
+        <v>2.7370748664</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1621665934832427</v>
+        <v>0.1637602869529148</v>
       </c>
       <c r="T39">
-        <v>1.516646808988113</v>
+        <v>1.537417977438888</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.09791261534997</v>
+        <v>4.963757020209181</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1179222979108072</v>
+        <v>0.1177200619271715</v>
       </c>
       <c r="C40">
-        <v>13.94053930721502</v>
+        <v>13.77931143655483</v>
       </c>
       <c r="D40">
-        <v>15.85093930721502</v>
+        <v>15.89551143655483</v>
       </c>
       <c r="E40">
-        <v>-2.8796</v>
+        <v>-2.6738</v>
       </c>
       <c r="F40">
-        <v>7.820399999999999</v>
+        <v>8.026199999999999</v>
       </c>
       <c r="G40">
         <v>5.91</v>
@@ -4567,28 +4567,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M40">
-        <v>0.43246812</v>
+        <v>0.44384886</v>
       </c>
       <c r="N40">
-        <v>1.714198546666666</v>
+        <v>1.702817806666667</v>
       </c>
       <c r="O40">
-        <v>0.3771236802666666</v>
+        <v>0.3746199174666667</v>
       </c>
       <c r="P40">
-        <v>1.3370748664</v>
+        <v>1.3281978892</v>
       </c>
       <c r="Q40">
-        <v>2.7370748664</v>
+        <v>2.7281978892</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1637602869529148</v>
+        <v>0.1654062326674942</v>
       </c>
       <c r="T40">
-        <v>1.537417977438888</v>
+        <v>1.558870167806083</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.963757020209181</v>
+        <v>4.836481199178177</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1177200619271715</v>
+        <v>0.1175178259435357</v>
       </c>
       <c r="C41">
-        <v>13.77931143655483</v>
+        <v>13.61833494240532</v>
       </c>
       <c r="D41">
-        <v>15.89551143655483</v>
+        <v>15.94033494240532</v>
       </c>
       <c r="E41">
-        <v>-2.6738</v>
+        <v>-2.468</v>
       </c>
       <c r="F41">
-        <v>8.026199999999999</v>
+        <v>8.231999999999999</v>
       </c>
       <c r="G41">
         <v>5.91</v>
@@ -4649,28 +4649,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M41">
-        <v>0.44384886</v>
+        <v>0.4552296</v>
       </c>
       <c r="N41">
-        <v>1.702817806666667</v>
+        <v>1.691437066666666</v>
       </c>
       <c r="O41">
-        <v>0.3746199174666667</v>
+        <v>0.3721161546666666</v>
       </c>
       <c r="P41">
-        <v>1.3281978892</v>
+        <v>1.319320912</v>
       </c>
       <c r="Q41">
-        <v>2.7281978892</v>
+        <v>2.719320912</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1654062326674942</v>
+        <v>0.1671070432392262</v>
       </c>
       <c r="T41">
-        <v>1.558870167806083</v>
+        <v>1.581037431185518</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.836481199178177</v>
+        <v>4.715569169198722</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1175178259435357</v>
+        <v>0.1173155899599</v>
       </c>
       <c r="C42">
-        <v>13.61833494240532</v>
+        <v>13.45761195733826</v>
       </c>
       <c r="D42">
-        <v>15.94033494240532</v>
+        <v>15.98541195733826</v>
       </c>
       <c r="E42">
-        <v>-2.468</v>
+        <v>-2.2622</v>
       </c>
       <c r="F42">
-        <v>8.231999999999999</v>
+        <v>8.437799999999999</v>
       </c>
       <c r="G42">
         <v>5.91</v>
@@ -4731,28 +4731,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M42">
-        <v>0.4552296</v>
+        <v>0.46661034</v>
       </c>
       <c r="N42">
-        <v>1.691437066666666</v>
+        <v>1.680056326666667</v>
       </c>
       <c r="O42">
-        <v>0.3721161546666666</v>
+        <v>0.3696123918666667</v>
       </c>
       <c r="P42">
-        <v>1.319320912</v>
+        <v>1.3104439348</v>
       </c>
       <c r="Q42">
-        <v>2.719320912</v>
+        <v>2.7104439348</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1671070432392262</v>
+        <v>0.1688655084066102</v>
       </c>
       <c r="T42">
-        <v>1.581037431185518</v>
+        <v>1.603956127221882</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.715569169198722</v>
+        <v>4.600555287023144</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1173155899599</v>
+        <v>0.1179323539762643</v>
       </c>
       <c r="C43">
-        <v>13.45761195733826</v>
+        <v>13.11512950711225</v>
       </c>
       <c r="D43">
-        <v>15.98541195733826</v>
+        <v>15.84872950711225</v>
       </c>
       <c r="E43">
-        <v>-2.2622</v>
+        <v>-2.0564</v>
       </c>
       <c r="F43">
-        <v>8.437799999999999</v>
+        <v>8.643599999999999</v>
       </c>
       <c r="G43">
         <v>5.91</v>
@@ -4813,45 +4813,45 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M43">
-        <v>0.46661034</v>
+        <v>0.49960008</v>
       </c>
       <c r="N43">
-        <v>1.680056326666667</v>
+        <v>1.647066586666666</v>
       </c>
       <c r="O43">
-        <v>0.3696123918666667</v>
+        <v>0.3623546490666666</v>
       </c>
       <c r="P43">
-        <v>1.3104439348</v>
+        <v>1.2847119376</v>
       </c>
       <c r="Q43">
-        <v>2.7104439348</v>
+        <v>2.6847119376</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1688655084066102</v>
+        <v>0.1706846103039039</v>
       </c>
       <c r="T43">
-        <v>1.603956127221882</v>
+        <v>1.62766512312157</v>
       </c>
       <c r="U43">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0.22</v>
       </c>
       <c r="W43">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.600555287023144</v>
+        <v>4.296770061899643</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1179323539762643</v>
+        <v>0.1177496179926286</v>
       </c>
       <c r="C44">
-        <v>13.11512950711225</v>
+        <v>12.94958174550711</v>
       </c>
       <c r="D44">
-        <v>15.84872950711225</v>
+        <v>15.8889817455071</v>
       </c>
       <c r="E44">
-        <v>-2.0564</v>
+        <v>-1.8506</v>
       </c>
       <c r="F44">
-        <v>8.643599999999999</v>
+        <v>8.849399999999999</v>
       </c>
       <c r="G44">
         <v>5.91</v>
@@ -4895,28 +4895,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M44">
-        <v>0.49960008</v>
+        <v>0.51149532</v>
       </c>
       <c r="N44">
-        <v>1.647066586666666</v>
+        <v>1.635171346666667</v>
       </c>
       <c r="O44">
-        <v>0.3623546490666666</v>
+        <v>0.3597376962666667</v>
       </c>
       <c r="P44">
-        <v>1.2847119376</v>
+        <v>1.2754336504</v>
       </c>
       <c r="Q44">
-        <v>2.6847119376</v>
+        <v>2.6754336504</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1706846103039039</v>
+        <v>0.1725675403379448</v>
       </c>
       <c r="T44">
-        <v>1.62766512312157</v>
+        <v>1.652206013614229</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.296770061899643</v>
+        <v>4.196845176739187</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1177496179926286</v>
+        <v>0.1175668820089928</v>
       </c>
       <c r="C45">
-        <v>12.94958174550711</v>
+        <v>12.78423896793279</v>
       </c>
       <c r="D45">
-        <v>15.8889817455071</v>
+        <v>15.92943896793279</v>
       </c>
       <c r="E45">
-        <v>-1.8506</v>
+        <v>-1.6448</v>
       </c>
       <c r="F45">
-        <v>8.849399999999999</v>
+        <v>9.055199999999999</v>
       </c>
       <c r="G45">
         <v>5.91</v>
@@ -4977,28 +4977,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M45">
-        <v>0.51149532</v>
+        <v>0.5233905599999999</v>
       </c>
       <c r="N45">
-        <v>1.635171346666667</v>
+        <v>1.623276106666667</v>
       </c>
       <c r="O45">
-        <v>0.3597376962666667</v>
+        <v>0.3571207434666667</v>
       </c>
       <c r="P45">
-        <v>1.2754336504</v>
+        <v>1.2661553632</v>
       </c>
       <c r="Q45">
-        <v>2.6754336504</v>
+        <v>2.6661553632</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1725675403379448</v>
+        <v>0.1745177178732015</v>
       </c>
       <c r="T45">
-        <v>1.652206013614229</v>
+        <v>1.677623364481626</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.196845176739187</v>
+        <v>4.101462331813296</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1175668820089928</v>
+        <v>0.1173841460253571</v>
       </c>
       <c r="C46">
-        <v>12.78423896793279</v>
+        <v>12.61910274420441</v>
       </c>
       <c r="D46">
-        <v>15.92943896793279</v>
+        <v>15.97010274420441</v>
       </c>
       <c r="E46">
-        <v>-1.6448</v>
+        <v>-1.439</v>
       </c>
       <c r="F46">
-        <v>9.055199999999999</v>
+        <v>9.260999999999999</v>
       </c>
       <c r="G46">
         <v>5.91</v>
@@ -5059,28 +5059,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M46">
-        <v>0.5233905599999999</v>
+        <v>0.5352858</v>
       </c>
       <c r="N46">
-        <v>1.623276106666667</v>
+        <v>1.611380866666666</v>
       </c>
       <c r="O46">
-        <v>0.3571207434666667</v>
+        <v>0.3545037906666667</v>
       </c>
       <c r="P46">
-        <v>1.2661553632</v>
+        <v>1.256877076</v>
       </c>
       <c r="Q46">
-        <v>2.6661553632</v>
+        <v>2.656877076</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1745177178732015</v>
+        <v>0.1765388109551947</v>
       </c>
       <c r="T46">
-        <v>1.677623364481626</v>
+        <v>1.703964982653291</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.101462331813296</v>
+        <v>4.010318724439666</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1173841460253571</v>
+        <v>0.1184572100417214</v>
       </c>
       <c r="C47">
-        <v>12.61910274420441</v>
+        <v>12.17744256484154</v>
       </c>
       <c r="D47">
-        <v>15.97010274420441</v>
+        <v>15.73424256484154</v>
       </c>
       <c r="E47">
-        <v>-1.439</v>
+        <v>-1.2332</v>
       </c>
       <c r="F47">
-        <v>9.260999999999999</v>
+        <v>9.466799999999999</v>
       </c>
       <c r="G47">
         <v>5.91</v>
@@ -5141,45 +5141,45 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M47">
-        <v>0.5352858</v>
+        <v>0.58031484</v>
       </c>
       <c r="N47">
-        <v>1.611380866666666</v>
+        <v>1.566351826666667</v>
       </c>
       <c r="O47">
-        <v>0.3545037906666667</v>
+        <v>0.3445974018666667</v>
       </c>
       <c r="P47">
-        <v>1.256877076</v>
+        <v>1.2217544248</v>
       </c>
       <c r="Q47">
-        <v>2.656877076</v>
+        <v>2.6217544248</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1765388109551947</v>
+        <v>0.1786347593365211</v>
       </c>
       <c r="T47">
-        <v>1.703964982653291</v>
+        <v>1.731282216312796</v>
       </c>
       <c r="U47">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V47">
         <v>0.22</v>
       </c>
       <c r="W47">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.010318724439666</v>
+        <v>3.699141429274265</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1184572100417214</v>
+        <v>0.1183017740580857</v>
       </c>
       <c r="C48">
-        <v>12.17744256484154</v>
+        <v>12.00537508382611</v>
       </c>
       <c r="D48">
-        <v>15.73424256484154</v>
+        <v>15.76797508382611</v>
       </c>
       <c r="E48">
-        <v>-1.2332</v>
+        <v>-1.0274</v>
       </c>
       <c r="F48">
-        <v>9.466799999999999</v>
+        <v>9.672599999999999</v>
       </c>
       <c r="G48">
         <v>5.91</v>
@@ -5223,28 +5223,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M48">
-        <v>0.58031484</v>
+        <v>0.59293038</v>
       </c>
       <c r="N48">
-        <v>1.566351826666667</v>
+        <v>1.553736286666667</v>
       </c>
       <c r="O48">
-        <v>0.3445974018666667</v>
+        <v>0.3418219830666667</v>
       </c>
       <c r="P48">
-        <v>1.2217544248</v>
+        <v>1.2119143036</v>
       </c>
       <c r="Q48">
-        <v>2.6217544248</v>
+        <v>2.6119143036</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1786347593365211</v>
+        <v>0.1808098001095956</v>
       </c>
       <c r="T48">
-        <v>1.731282216312796</v>
+        <v>1.759630288978321</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.699141429274265</v>
+        <v>3.620436292481196</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1183017740580857</v>
+        <v>0.11814633807445</v>
       </c>
       <c r="C49">
-        <v>12.00537508382611</v>
+        <v>11.83345255132938</v>
       </c>
       <c r="D49">
-        <v>15.76797508382611</v>
+        <v>15.80185255132938</v>
       </c>
       <c r="E49">
-        <v>-1.0274</v>
+        <v>-0.8216000000000001</v>
       </c>
       <c r="F49">
-        <v>9.672599999999999</v>
+        <v>9.878399999999999</v>
       </c>
       <c r="G49">
         <v>5.91</v>
@@ -5305,28 +5305,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M49">
-        <v>0.59293038</v>
+        <v>0.60554592</v>
       </c>
       <c r="N49">
-        <v>1.553736286666667</v>
+        <v>1.541120746666667</v>
       </c>
       <c r="O49">
-        <v>0.3418219830666667</v>
+        <v>0.3390465642666666</v>
       </c>
       <c r="P49">
-        <v>1.2119143036</v>
+        <v>1.2020741824</v>
       </c>
       <c r="Q49">
-        <v>2.6119143036</v>
+        <v>2.6020741824</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1808098001095956</v>
+        <v>0.1830684962970191</v>
       </c>
       <c r="T49">
-        <v>1.759630288978321</v>
+        <v>1.789068672130981</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.620436292481196</v>
+        <v>3.545010536387838</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.11814633807445</v>
+        <v>0.1190610620908142</v>
       </c>
       <c r="C50">
-        <v>11.83345255132938</v>
+        <v>11.43035355484704</v>
       </c>
       <c r="D50">
-        <v>15.80185255132938</v>
+        <v>15.60455355484704</v>
       </c>
       <c r="E50">
-        <v>-0.8216000000000001</v>
+        <v>-0.6158000000000001</v>
       </c>
       <c r="F50">
-        <v>9.878399999999999</v>
+        <v>10.0842</v>
       </c>
       <c r="G50">
         <v>5.91</v>
@@ -5387,45 +5387,45 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M50">
-        <v>0.60554592</v>
+        <v>0.64639722</v>
       </c>
       <c r="N50">
-        <v>1.541120746666667</v>
+        <v>1.500269446666667</v>
       </c>
       <c r="O50">
-        <v>0.3390465642666666</v>
+        <v>0.3300592782666666</v>
       </c>
       <c r="P50">
-        <v>1.2020741824</v>
+        <v>1.1702101684</v>
       </c>
       <c r="Q50">
-        <v>2.6020741824</v>
+        <v>2.5702101684</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1830684962970191</v>
+        <v>0.1854157688055181</v>
       </c>
       <c r="T50">
-        <v>1.789068672130981</v>
+        <v>1.819661501681784</v>
       </c>
       <c r="U50">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V50">
         <v>0.22</v>
       </c>
       <c r="W50">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.545010536387838</v>
+        <v>3.320971378352566</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1190610620908142</v>
+        <v>0.1189274661071785</v>
       </c>
       <c r="C51">
-        <v>11.43035355484704</v>
+        <v>11.25306138907585</v>
       </c>
       <c r="D51">
-        <v>15.60455355484704</v>
+        <v>15.63306138907585</v>
       </c>
       <c r="E51">
-        <v>-0.6158000000000001</v>
+        <v>-0.4100000000000001</v>
       </c>
       <c r="F51">
-        <v>10.0842</v>
+        <v>10.29</v>
       </c>
       <c r="G51">
         <v>5.91</v>
@@ -5469,28 +5469,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M51">
-        <v>0.64639722</v>
+        <v>0.659589</v>
       </c>
       <c r="N51">
-        <v>1.500269446666667</v>
+        <v>1.487077666666667</v>
       </c>
       <c r="O51">
-        <v>0.3300592782666666</v>
+        <v>0.3271570866666667</v>
       </c>
       <c r="P51">
-        <v>1.1702101684</v>
+        <v>1.15992058</v>
       </c>
       <c r="Q51">
-        <v>2.5702101684</v>
+        <v>2.55992058</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1854157688055181</v>
+        <v>0.187856932214357</v>
       </c>
       <c r="T51">
-        <v>1.819661501681784</v>
+        <v>1.851478044414619</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.320971378352566</v>
+        <v>3.254551950785514</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1189274661071785</v>
+        <v>0.1187938701235428</v>
       </c>
       <c r="C52">
-        <v>11.25306138907585</v>
+        <v>11.07587357541392</v>
       </c>
       <c r="D52">
-        <v>15.63306138907585</v>
+        <v>15.66167357541391</v>
       </c>
       <c r="E52">
-        <v>-0.4100000000000001</v>
+        <v>-0.2042000000000002</v>
       </c>
       <c r="F52">
-        <v>10.29</v>
+        <v>10.4958</v>
       </c>
       <c r="G52">
         <v>5.91</v>
@@ -5551,28 +5551,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M52">
-        <v>0.659589</v>
+        <v>0.67278078</v>
       </c>
       <c r="N52">
-        <v>1.487077666666667</v>
+        <v>1.473885886666666</v>
       </c>
       <c r="O52">
-        <v>0.3271570866666667</v>
+        <v>0.3242548950666666</v>
       </c>
       <c r="P52">
-        <v>1.15992058</v>
+        <v>1.1496309916</v>
       </c>
       <c r="Q52">
-        <v>2.55992058</v>
+        <v>2.5496309916</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.187856932214357</v>
+        <v>0.1903977349460057</v>
       </c>
       <c r="T52">
-        <v>1.851478044414619</v>
+        <v>1.884593221544714</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.254551950785514</v>
+        <v>3.190737206652465</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1187938701235428</v>
+        <v>0.1186602741399071</v>
       </c>
       <c r="C53">
-        <v>11.07587357541392</v>
+        <v>10.89879068787867</v>
       </c>
       <c r="D53">
-        <v>15.66167357541391</v>
+        <v>15.69039068787867</v>
       </c>
       <c r="E53">
-        <v>-0.2042000000000002</v>
+        <v>0.001599999999999824</v>
       </c>
       <c r="F53">
-        <v>10.4958</v>
+        <v>10.7016</v>
       </c>
       <c r="G53">
         <v>5.91</v>
@@ -5633,28 +5633,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M53">
-        <v>0.67278078</v>
+        <v>0.68597256</v>
       </c>
       <c r="N53">
-        <v>1.473885886666666</v>
+        <v>1.460694106666667</v>
       </c>
       <c r="O53">
-        <v>0.3242548950666666</v>
+        <v>0.3213527034666667</v>
       </c>
       <c r="P53">
-        <v>1.1496309916</v>
+        <v>1.1393414032</v>
       </c>
       <c r="Q53">
-        <v>2.5496309916</v>
+        <v>2.5393414032</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1903977349460057</v>
+        <v>0.1930444044581397</v>
       </c>
       <c r="T53">
-        <v>1.884593221544714</v>
+        <v>1.919088197721895</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.190737206652465</v>
+        <v>3.129376875755302</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1186602741399071</v>
+        <v>0.1185266781562714</v>
       </c>
       <c r="C54">
-        <v>10.89879068787867</v>
+        <v>10.72181330470536</v>
       </c>
       <c r="D54">
-        <v>15.69039068787867</v>
+        <v>15.71921330470536</v>
       </c>
       <c r="E54">
-        <v>0.001599999999999824</v>
+        <v>0.2073999999999998</v>
       </c>
       <c r="F54">
-        <v>10.7016</v>
+        <v>10.9074</v>
       </c>
       <c r="G54">
         <v>5.91</v>
@@ -5715,28 +5715,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M54">
-        <v>0.68597256</v>
+        <v>0.6991643399999999</v>
       </c>
       <c r="N54">
-        <v>1.460694106666667</v>
+        <v>1.447502326666667</v>
       </c>
       <c r="O54">
-        <v>0.3213527034666667</v>
+        <v>0.3184505118666667</v>
       </c>
       <c r="P54">
-        <v>1.1393414032</v>
+        <v>1.1290518148</v>
       </c>
       <c r="Q54">
-        <v>2.5393414032</v>
+        <v>2.5290518148</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1930444044581397</v>
+        <v>0.1958036982048326</v>
       </c>
       <c r="T54">
-        <v>1.919088197721895</v>
+        <v>1.955051045225765</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.129376875755302</v>
+        <v>3.070332029042938</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1185266781562714</v>
+        <v>0.1183930821726356</v>
       </c>
       <c r="C55">
-        <v>10.72181330470536</v>
+        <v>10.5449420083858</v>
       </c>
       <c r="D55">
-        <v>15.71921330470536</v>
+        <v>15.7481420083858</v>
       </c>
       <c r="E55">
-        <v>0.2073999999999998</v>
+        <v>0.4131999999999998</v>
       </c>
       <c r="F55">
-        <v>10.9074</v>
+        <v>11.1132</v>
       </c>
       <c r="G55">
         <v>5.91</v>
@@ -5797,28 +5797,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M55">
-        <v>0.6991643399999999</v>
+        <v>0.71235612</v>
       </c>
       <c r="N55">
-        <v>1.447502326666667</v>
+        <v>1.434310546666667</v>
       </c>
       <c r="O55">
-        <v>0.3184505118666667</v>
+        <v>0.3155483202666666</v>
       </c>
       <c r="P55">
-        <v>1.1290518148</v>
+        <v>1.1187622264</v>
       </c>
       <c r="Q55">
-        <v>2.5290518148</v>
+        <v>2.5187622264</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1958036982048326</v>
+        <v>0.19868296124486</v>
       </c>
       <c r="T55">
-        <v>1.955051045225765</v>
+        <v>1.992577494795021</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.070332029042938</v>
+        <v>3.013474028505106</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1183930821726356</v>
+        <v>0.1216056861889999</v>
       </c>
       <c r="C56">
-        <v>10.5449420083858</v>
+        <v>9.67174426014463</v>
       </c>
       <c r="D56">
-        <v>15.7481420083858</v>
+        <v>15.08074426014463</v>
       </c>
       <c r="E56">
-        <v>0.4131999999999998</v>
+        <v>0.6190000000000015</v>
       </c>
       <c r="F56">
-        <v>11.1132</v>
+        <v>11.319</v>
       </c>
       <c r="G56">
         <v>5.91</v>
@@ -5879,45 +5879,45 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M56">
-        <v>0.71235612</v>
+        <v>0.8138361000000002</v>
       </c>
       <c r="N56">
-        <v>1.434310546666667</v>
+        <v>1.332830566666666</v>
       </c>
       <c r="O56">
-        <v>0.3155483202666666</v>
+        <v>0.2932227246666666</v>
       </c>
       <c r="P56">
-        <v>1.1187622264</v>
+        <v>1.039607842</v>
       </c>
       <c r="Q56">
-        <v>2.5187622264</v>
+        <v>2.439607842</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.19868296124486</v>
+        <v>0.2016901915311109</v>
       </c>
       <c r="T56">
-        <v>1.992577494795021</v>
+        <v>2.031771786567354</v>
       </c>
       <c r="U56">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V56">
         <v>0.22</v>
       </c>
       <c r="W56">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.013474028505106</v>
+        <v>2.637713744409552</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1216056861889999</v>
+        <v>0.1215329302053642</v>
       </c>
       <c r="C57">
-        <v>9.67174426014463</v>
+        <v>9.480432203231347</v>
       </c>
       <c r="D57">
-        <v>15.08074426014463</v>
+        <v>15.09523220323135</v>
       </c>
       <c r="E57">
-        <v>0.6190000000000015</v>
+        <v>0.8248000000000015</v>
       </c>
       <c r="F57">
-        <v>11.319</v>
+        <v>11.5248</v>
       </c>
       <c r="G57">
         <v>5.91</v>
@@ -5961,28 +5961,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M57">
-        <v>0.8138361000000002</v>
+        <v>0.8286331200000001</v>
       </c>
       <c r="N57">
-        <v>1.332830566666666</v>
+        <v>1.318033546666666</v>
       </c>
       <c r="O57">
-        <v>0.2932227246666666</v>
+        <v>0.2899673802666666</v>
       </c>
       <c r="P57">
-        <v>1.039607842</v>
+        <v>1.0280661664</v>
       </c>
       <c r="Q57">
-        <v>2.439607842</v>
+        <v>2.4280661664</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2016901915311109</v>
+        <v>0.2048341141031004</v>
       </c>
       <c r="T57">
-        <v>2.031771786567354</v>
+        <v>2.072747637056612</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.637713744409552</v>
+        <v>2.590611713259381</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1215329302053642</v>
+        <v>0.1214601742217285</v>
       </c>
       <c r="C58">
-        <v>9.480432203231347</v>
+        <v>9.289148009974491</v>
       </c>
       <c r="D58">
-        <v>15.09523220323135</v>
+        <v>15.10974800997449</v>
       </c>
       <c r="E58">
-        <v>0.8248000000000015</v>
+        <v>1.030600000000002</v>
       </c>
       <c r="F58">
-        <v>11.5248</v>
+        <v>11.7306</v>
       </c>
       <c r="G58">
         <v>5.91</v>
@@ -6043,28 +6043,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M58">
-        <v>0.8286331200000001</v>
+        <v>0.8434301400000002</v>
       </c>
       <c r="N58">
-        <v>1.318033546666666</v>
+        <v>1.303236526666666</v>
       </c>
       <c r="O58">
-        <v>0.2899673802666666</v>
+        <v>0.2867120358666666</v>
       </c>
       <c r="P58">
-        <v>1.0280661664</v>
+        <v>1.0165244908</v>
       </c>
       <c r="Q58">
-        <v>2.4280661664</v>
+        <v>2.4165244908</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2048341141031004</v>
+        <v>0.2081242656319267</v>
       </c>
       <c r="T58">
-        <v>2.072747637056612</v>
+        <v>2.115629341056998</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.590611713259381</v>
+        <v>2.545162384956585</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1214601742217285</v>
+        <v>0.1213874182380927</v>
       </c>
       <c r="C59">
-        <v>9.289148009974491</v>
+        <v>9.097891760833809</v>
       </c>
       <c r="D59">
-        <v>15.10974800997449</v>
+        <v>15.12429176083381</v>
       </c>
       <c r="E59">
-        <v>1.030600000000002</v>
+        <v>1.236400000000001</v>
       </c>
       <c r="F59">
-        <v>11.7306</v>
+        <v>11.9364</v>
       </c>
       <c r="G59">
         <v>5.91</v>
@@ -6125,28 +6125,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M59">
-        <v>0.8434301400000002</v>
+        <v>0.8582271600000001</v>
       </c>
       <c r="N59">
-        <v>1.303236526666666</v>
+        <v>1.288439506666666</v>
       </c>
       <c r="O59">
-        <v>0.2867120358666666</v>
+        <v>0.2834566914666666</v>
       </c>
       <c r="P59">
-        <v>1.0165244908</v>
+        <v>1.0049828152</v>
       </c>
       <c r="Q59">
-        <v>2.4165244908</v>
+        <v>2.4049828152</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2081242656319267</v>
+        <v>0.2115710910430779</v>
       </c>
       <c r="T59">
-        <v>2.115629341056998</v>
+        <v>2.160553030962165</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.545162384956585</v>
+        <v>2.501280274871126</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1213874182380927</v>
+        <v>0.123109442254457</v>
       </c>
       <c r="C60">
-        <v>9.097891760833811</v>
+        <v>8.555206732522091</v>
       </c>
       <c r="D60">
-        <v>15.12429176083381</v>
+        <v>14.78740673252209</v>
       </c>
       <c r="E60">
-        <v>1.2364</v>
+        <v>1.4422</v>
       </c>
       <c r="F60">
-        <v>11.9364</v>
+        <v>12.1422</v>
       </c>
       <c r="G60">
         <v>5.91</v>
@@ -6207,45 +6207,45 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M60">
-        <v>0.85822716</v>
+        <v>0.92037876</v>
       </c>
       <c r="N60">
-        <v>1.288439506666667</v>
+        <v>1.226287906666667</v>
       </c>
       <c r="O60">
-        <v>0.2834566914666666</v>
+        <v>0.2697833394666667</v>
       </c>
       <c r="P60">
-        <v>1.0049828152</v>
+        <v>0.9565045671999999</v>
       </c>
       <c r="Q60">
-        <v>2.4049828152</v>
+        <v>2.3565045672</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2115710910430779</v>
+        <v>0.2151860542791634</v>
       </c>
       <c r="T60">
-        <v>2.160553030962164</v>
+        <v>2.207668120374899</v>
       </c>
       <c r="U60">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V60">
         <v>0.22</v>
       </c>
       <c r="W60">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.501280274871127</v>
+        <v>2.332373105466565</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.123109442254457</v>
+        <v>0.1230671062708213</v>
       </c>
       <c r="C61">
-        <v>8.555206732522091</v>
+        <v>8.357509008376041</v>
       </c>
       <c r="D61">
-        <v>14.78740673252209</v>
+        <v>14.79550900837604</v>
       </c>
       <c r="E61">
-        <v>1.4422</v>
+        <v>1.648</v>
       </c>
       <c r="F61">
-        <v>12.1422</v>
+        <v>12.348</v>
       </c>
       <c r="G61">
         <v>5.91</v>
@@ -6289,28 +6289,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M61">
-        <v>0.92037876</v>
+        <v>0.9359784</v>
       </c>
       <c r="N61">
-        <v>1.226287906666667</v>
+        <v>1.210688266666667</v>
       </c>
       <c r="O61">
-        <v>0.2697833394666667</v>
+        <v>0.2663514186666666</v>
       </c>
       <c r="P61">
-        <v>0.9565045671999999</v>
+        <v>0.9443368479999998</v>
       </c>
       <c r="Q61">
-        <v>2.3565045672</v>
+        <v>2.344336848</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2151860542791634</v>
+        <v>0.2189817656770532</v>
       </c>
       <c r="T61">
-        <v>2.207668120374899</v>
+        <v>2.257138964258272</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.332373105466565</v>
+        <v>2.293500220375456</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1230671062708213</v>
+        <v>0.1230247702871856</v>
       </c>
       <c r="C62">
-        <v>8.357509008376041</v>
+        <v>8.159820167851574</v>
       </c>
       <c r="D62">
-        <v>14.79550900837604</v>
+        <v>14.80362016785157</v>
       </c>
       <c r="E62">
-        <v>1.648</v>
+        <v>1.8538</v>
       </c>
       <c r="F62">
-        <v>12.348</v>
+        <v>12.5538</v>
       </c>
       <c r="G62">
         <v>5.91</v>
@@ -6371,28 +6371,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M62">
-        <v>0.9359784</v>
+        <v>0.95157804</v>
       </c>
       <c r="N62">
-        <v>1.210688266666667</v>
+        <v>1.195088626666666</v>
       </c>
       <c r="O62">
-        <v>0.2663514186666666</v>
+        <v>0.2629194978666666</v>
       </c>
       <c r="P62">
-        <v>0.9443368479999998</v>
+        <v>0.9321691287999998</v>
       </c>
       <c r="Q62">
-        <v>2.344336848</v>
+        <v>2.3321691288</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2189817656770532</v>
+        <v>0.2229721289415014</v>
       </c>
       <c r="T62">
-        <v>2.257138964258272</v>
+        <v>2.309146774494637</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.293500220375456</v>
+        <v>2.255901856107005</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1230247702871856</v>
+        <v>0.1229824343035498</v>
       </c>
       <c r="C63">
-        <v>8.159820167851574</v>
+        <v>7.962140225567179</v>
       </c>
       <c r="D63">
-        <v>14.80362016785157</v>
+        <v>14.81174022556718</v>
       </c>
       <c r="E63">
-        <v>1.8538</v>
+        <v>2.0596</v>
       </c>
       <c r="F63">
-        <v>12.5538</v>
+        <v>12.7596</v>
       </c>
       <c r="G63">
         <v>5.91</v>
@@ -6453,28 +6453,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M63">
-        <v>0.95157804</v>
+        <v>0.96717768</v>
       </c>
       <c r="N63">
-        <v>1.195088626666666</v>
+        <v>1.179488986666666</v>
       </c>
       <c r="O63">
-        <v>0.2629194978666666</v>
+        <v>0.2594875770666666</v>
       </c>
       <c r="P63">
-        <v>0.9321691287999998</v>
+        <v>0.9200014095999998</v>
       </c>
       <c r="Q63">
-        <v>2.3321691288</v>
+        <v>2.3200014096</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2229721289415014</v>
+        <v>0.2271725113251311</v>
       </c>
       <c r="T63">
-        <v>2.309146774494637</v>
+        <v>2.363891837901338</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.255901856107005</v>
+        <v>2.219516342298828</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1229824343035498</v>
+        <v>0.1229400983199141</v>
       </c>
       <c r="C64">
-        <v>7.962140225567179</v>
+        <v>7.764469196173433</v>
       </c>
       <c r="D64">
-        <v>14.81174022556718</v>
+        <v>14.81986919617343</v>
       </c>
       <c r="E64">
-        <v>2.0596</v>
+        <v>2.2654</v>
       </c>
       <c r="F64">
-        <v>12.7596</v>
+        <v>12.9654</v>
       </c>
       <c r="G64">
         <v>5.91</v>
@@ -6535,28 +6535,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M64">
-        <v>0.96717768</v>
+        <v>0.98277732</v>
       </c>
       <c r="N64">
-        <v>1.179488986666666</v>
+        <v>1.163889346666667</v>
       </c>
       <c r="O64">
-        <v>0.2594875770666666</v>
+        <v>0.2560556562666667</v>
       </c>
       <c r="P64">
-        <v>0.9200014095999998</v>
+        <v>0.9078336903999999</v>
       </c>
       <c r="Q64">
-        <v>2.3200014096</v>
+        <v>2.3078336904</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2271725113251311</v>
+        <v>0.2315999414051733</v>
       </c>
       <c r="T64">
-        <v>2.363891837901338</v>
+        <v>2.421596093924617</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.219516342298828</v>
+        <v>2.184285924167101</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1229400983199141</v>
+        <v>0.1228977623362784</v>
       </c>
       <c r="C65">
-        <v>7.764469196173433</v>
+        <v>7.566807094353102</v>
       </c>
       <c r="D65">
-        <v>14.81986919617343</v>
+        <v>14.8280070943531</v>
       </c>
       <c r="E65">
-        <v>2.2654</v>
+        <v>2.4712</v>
       </c>
       <c r="F65">
-        <v>12.9654</v>
+        <v>13.1712</v>
       </c>
       <c r="G65">
         <v>5.91</v>
@@ -6617,28 +6617,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M65">
-        <v>0.98277732</v>
+        <v>0.99837696</v>
       </c>
       <c r="N65">
-        <v>1.163889346666667</v>
+        <v>1.148289706666667</v>
       </c>
       <c r="O65">
-        <v>0.2560556562666667</v>
+        <v>0.2526237354666667</v>
       </c>
       <c r="P65">
-        <v>0.9078336903999999</v>
+        <v>0.8956659711999999</v>
       </c>
       <c r="Q65">
-        <v>2.3078336904</v>
+        <v>2.2956659712</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2315999414051733</v>
+        <v>0.2362733398229955</v>
       </c>
       <c r="T65">
-        <v>2.421596093924617</v>
+        <v>2.48250614194919</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.184285924167101</v>
+        <v>2.15015645660199</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1228977623362784</v>
+        <v>0.1228554263526427</v>
       </c>
       <c r="C66">
-        <v>7.566807094353102</v>
+        <v>7.369153934821203</v>
       </c>
       <c r="D66">
-        <v>14.8280070943531</v>
+        <v>14.8361539348212</v>
       </c>
       <c r="E66">
-        <v>2.4712</v>
+        <v>2.677</v>
       </c>
       <c r="F66">
-        <v>13.1712</v>
+        <v>13.377</v>
       </c>
       <c r="G66">
         <v>5.91</v>
@@ -6699,28 +6699,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M66">
-        <v>0.99837696</v>
+        <v>1.0139766</v>
       </c>
       <c r="N66">
-        <v>1.148289706666667</v>
+        <v>1.132690066666667</v>
       </c>
       <c r="O66">
-        <v>0.2526237354666667</v>
+        <v>0.2491918146666667</v>
       </c>
       <c r="P66">
-        <v>0.8956659711999999</v>
+        <v>0.883498252</v>
       </c>
       <c r="Q66">
-        <v>2.2956659712</v>
+        <v>2.283498252</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2362733398229955</v>
+        <v>0.2412137895789791</v>
       </c>
       <c r="T66">
-        <v>2.48250614194919</v>
+        <v>2.546896764146596</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.15015645660199</v>
+        <v>2.117077126500421</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1228554263526427</v>
+        <v>0.1228130903690069</v>
       </c>
       <c r="C67">
-        <v>7.369153934821203</v>
+        <v>7.171509732325141</v>
       </c>
       <c r="D67">
-        <v>14.8361539348212</v>
+        <v>14.84430973232514</v>
       </c>
       <c r="E67">
-        <v>2.677</v>
+        <v>2.8828</v>
       </c>
       <c r="F67">
-        <v>13.377</v>
+        <v>13.5828</v>
       </c>
       <c r="G67">
         <v>5.91</v>
@@ -6781,28 +6781,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M67">
-        <v>1.0139766</v>
+        <v>1.02957624</v>
       </c>
       <c r="N67">
-        <v>1.132690066666667</v>
+        <v>1.117090426666667</v>
       </c>
       <c r="O67">
-        <v>0.2491918146666667</v>
+        <v>0.2457598938666667</v>
       </c>
       <c r="P67">
-        <v>0.883498252</v>
+        <v>0.8713305327999999</v>
       </c>
       <c r="Q67">
-        <v>2.283498252</v>
+        <v>2.2713305328</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2412137895789791</v>
+        <v>0.2464448540264911</v>
       </c>
       <c r="T67">
-        <v>2.546896764146596</v>
+        <v>2.615075070002672</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.117077126500421</v>
+        <v>2.085000200341323</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1228130903690069</v>
+        <v>0.1227707543853712</v>
       </c>
       <c r="C68">
-        <v>7.171509732325141</v>
+        <v>6.973874501644726</v>
       </c>
       <c r="D68">
-        <v>14.84430973232514</v>
+        <v>14.85247450164473</v>
       </c>
       <c r="E68">
-        <v>2.8828</v>
+        <v>3.0886</v>
       </c>
       <c r="F68">
-        <v>13.5828</v>
+        <v>13.7886</v>
       </c>
       <c r="G68">
         <v>5.91</v>
@@ -6863,28 +6863,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M68">
-        <v>1.02957624</v>
+        <v>1.04517588</v>
       </c>
       <c r="N68">
-        <v>1.117090426666667</v>
+        <v>1.101490786666667</v>
       </c>
       <c r="O68">
-        <v>0.2457598938666667</v>
+        <v>0.2423279730666666</v>
       </c>
       <c r="P68">
-        <v>0.8713305327999999</v>
+        <v>0.8591628135999999</v>
       </c>
       <c r="Q68">
-        <v>2.2713305328</v>
+        <v>2.2591628136</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2464448540264911</v>
+        <v>0.2519929526829431</v>
       </c>
       <c r="T68">
-        <v>2.615075070002672</v>
+        <v>2.68738539439548</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.085000200341323</v>
+        <v>2.05388079436608</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1227707543853712</v>
+        <v>0.1227284184017355</v>
       </c>
       <c r="C69">
-        <v>6.973874501644726</v>
+        <v>6.776248257592338</v>
       </c>
       <c r="D69">
-        <v>14.85247450164473</v>
+        <v>14.86064825759234</v>
       </c>
       <c r="E69">
-        <v>3.0886</v>
+        <v>3.294400000000001</v>
       </c>
       <c r="F69">
-        <v>13.7886</v>
+        <v>13.9944</v>
       </c>
       <c r="G69">
         <v>5.91</v>
@@ -6945,28 +6945,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M69">
-        <v>1.04517588</v>
+        <v>1.06077552</v>
       </c>
       <c r="N69">
-        <v>1.101490786666667</v>
+        <v>1.085891146666666</v>
       </c>
       <c r="O69">
-        <v>0.2423279730666666</v>
+        <v>0.2388960522666666</v>
       </c>
       <c r="P69">
-        <v>0.8591628135999999</v>
+        <v>0.8469950943999998</v>
       </c>
       <c r="Q69">
-        <v>2.2591628136</v>
+        <v>2.2469950944</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2519929526829431</v>
+        <v>0.2578878075054235</v>
       </c>
       <c r="T69">
-        <v>2.68738539439548</v>
+        <v>2.764215114062838</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.05388079436608</v>
+        <v>2.023676665037167</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1227284184017355</v>
+        <v>0.1303285224180998</v>
       </c>
       <c r="C70">
-        <v>6.776248257592338</v>
+        <v>5.234301957179541</v>
       </c>
       <c r="D70">
-        <v>14.86064825759234</v>
+        <v>13.52450195717954</v>
       </c>
       <c r="E70">
-        <v>3.294400000000001</v>
+        <v>3.500200000000001</v>
       </c>
       <c r="F70">
-        <v>13.9944</v>
+        <v>14.2002</v>
       </c>
       <c r="G70">
         <v>5.91</v>
@@ -7027,45 +7027,45 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M70">
-        <v>1.06077552</v>
+        <v>1.278018</v>
       </c>
       <c r="N70">
-        <v>1.085891146666666</v>
+        <v>0.8686486666666664</v>
       </c>
       <c r="O70">
-        <v>0.2388960522666666</v>
+        <v>0.1911027066666666</v>
       </c>
       <c r="P70">
-        <v>0.8469950943999998</v>
+        <v>0.6775459599999998</v>
       </c>
       <c r="Q70">
-        <v>2.2469950944</v>
+        <v>2.07754596</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2578878075054235</v>
+        <v>0.2641629755422574</v>
       </c>
       <c r="T70">
-        <v>2.764215114062838</v>
+        <v>2.846001589837768</v>
       </c>
       <c r="U70">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V70">
         <v>0.22</v>
       </c>
       <c r="W70">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.023676665037167</v>
+        <v>1.679684219366759</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1303285224180998</v>
+        <v>0.130396946434464</v>
       </c>
       <c r="C71">
-        <v>5.234301957179541</v>
+        <v>5.017563019283555</v>
       </c>
       <c r="D71">
-        <v>13.52450195717954</v>
+        <v>13.51356301928356</v>
       </c>
       <c r="E71">
-        <v>3.500200000000001</v>
+        <v>3.706000000000001</v>
       </c>
       <c r="F71">
-        <v>14.2002</v>
+        <v>14.406</v>
       </c>
       <c r="G71">
         <v>5.91</v>
@@ -7109,28 +7109,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M71">
-        <v>1.278018</v>
+        <v>1.29654</v>
       </c>
       <c r="N71">
-        <v>0.8686486666666664</v>
+        <v>0.8501266666666665</v>
       </c>
       <c r="O71">
-        <v>0.1911027066666666</v>
+        <v>0.1870278666666666</v>
       </c>
       <c r="P71">
-        <v>0.6775459599999998</v>
+        <v>0.6630987999999999</v>
       </c>
       <c r="Q71">
-        <v>2.07754596</v>
+        <v>2.0630988</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2641629755422574</v>
+        <v>0.2708564881148802</v>
       </c>
       <c r="T71">
-        <v>2.846001589837768</v>
+        <v>2.933240497331027</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.679684219366759</v>
+        <v>1.655688730518662</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.130396946434464</v>
+        <v>0.1304653704508283</v>
       </c>
       <c r="C72">
-        <v>5.017563019283555</v>
+        <v>4.800841762431455</v>
       </c>
       <c r="D72">
-        <v>13.51356301928356</v>
+        <v>13.50264176243146</v>
       </c>
       <c r="E72">
-        <v>3.706000000000001</v>
+        <v>3.911800000000001</v>
       </c>
       <c r="F72">
-        <v>14.406</v>
+        <v>14.6118</v>
       </c>
       <c r="G72">
         <v>5.91</v>
@@ -7191,28 +7191,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M72">
-        <v>1.29654</v>
+        <v>1.315062</v>
       </c>
       <c r="N72">
-        <v>0.8501266666666665</v>
+        <v>0.8316046666666665</v>
       </c>
       <c r="O72">
-        <v>0.1870278666666666</v>
+        <v>0.1829530266666666</v>
       </c>
       <c r="P72">
-        <v>0.6630987999999999</v>
+        <v>0.64865164</v>
       </c>
       <c r="Q72">
-        <v>2.0630988</v>
+        <v>2.04865164</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2708564881148802</v>
+        <v>0.2780116222442357</v>
       </c>
       <c r="T72">
-        <v>2.933240497331027</v>
+        <v>3.026495881203132</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.655688730518662</v>
+        <v>1.632369170933893</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1304653704508283</v>
+        <v>0.1305337944671926</v>
       </c>
       <c r="C73">
-        <v>4.800841762431457</v>
+        <v>4.584138143790007</v>
       </c>
       <c r="D73">
-        <v>13.50264176243146</v>
+        <v>13.49173814379</v>
       </c>
       <c r="E73">
-        <v>3.911799999999999</v>
+        <v>4.117599999999999</v>
       </c>
       <c r="F73">
-        <v>14.6118</v>
+        <v>14.8176</v>
       </c>
       <c r="G73">
         <v>5.91</v>
@@ -7273,28 +7273,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M73">
-        <v>1.315062</v>
+        <v>1.333584</v>
       </c>
       <c r="N73">
-        <v>0.8316046666666665</v>
+        <v>0.8130826666666666</v>
       </c>
       <c r="O73">
-        <v>0.1829530266666666</v>
+        <v>0.1788781866666667</v>
       </c>
       <c r="P73">
-        <v>0.64865164</v>
+        <v>0.63420448</v>
       </c>
       <c r="Q73">
-        <v>2.04865164</v>
+        <v>2.03420448</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2780116222442356</v>
+        <v>0.2856778373828308</v>
       </c>
       <c r="T73">
-        <v>3.02649588120313</v>
+        <v>3.126412363923242</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.632369170933893</v>
+        <v>1.609697376893144</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1305337944671926</v>
+        <v>0.1306022184835569</v>
       </c>
       <c r="C74">
-        <v>4.584138143790007</v>
+        <v>4.367452120664179</v>
       </c>
       <c r="D74">
-        <v>13.49173814379</v>
+        <v>13.48085212066418</v>
       </c>
       <c r="E74">
-        <v>4.117599999999999</v>
+        <v>4.323399999999999</v>
       </c>
       <c r="F74">
-        <v>14.8176</v>
+        <v>15.0234</v>
       </c>
       <c r="G74">
         <v>5.91</v>
@@ -7355,28 +7355,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M74">
-        <v>1.333584</v>
+        <v>1.352106</v>
       </c>
       <c r="N74">
-        <v>0.8130826666666666</v>
+        <v>0.7945606666666667</v>
       </c>
       <c r="O74">
-        <v>0.1788781866666667</v>
+        <v>0.1748033466666667</v>
       </c>
       <c r="P74">
-        <v>0.63420448</v>
+        <v>0.6197573200000001</v>
       </c>
       <c r="Q74">
-        <v>2.03420448</v>
+        <v>2.01975732</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2856778373828308</v>
+        <v>0.2939119203094699</v>
       </c>
       <c r="T74">
-        <v>3.126412363923242</v>
+        <v>3.233730067585583</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.609697376893144</v>
+        <v>1.587646727894608</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1306022184835569</v>
+        <v>0.1306706424999212</v>
       </c>
       <c r="C75">
-        <v>4.367452120664179</v>
+        <v>4.150783650496663</v>
       </c>
       <c r="D75">
-        <v>13.48085212066418</v>
+        <v>13.46998365049666</v>
       </c>
       <c r="E75">
-        <v>4.323399999999999</v>
+        <v>4.529199999999999</v>
       </c>
       <c r="F75">
-        <v>15.0234</v>
+        <v>15.2292</v>
       </c>
       <c r="G75">
         <v>5.91</v>
@@ -7437,28 +7437,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M75">
-        <v>1.352106</v>
+        <v>1.370628</v>
       </c>
       <c r="N75">
-        <v>0.7945606666666667</v>
+        <v>0.7760386666666668</v>
       </c>
       <c r="O75">
-        <v>0.1748033466666667</v>
+        <v>0.1707285066666667</v>
       </c>
       <c r="P75">
-        <v>0.6197573200000001</v>
+        <v>0.60531016</v>
       </c>
       <c r="Q75">
-        <v>2.01975732</v>
+        <v>2.00531016</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2939119203094699</v>
+        <v>0.302779394230466</v>
       </c>
       <c r="T75">
-        <v>3.233730067585583</v>
+        <v>3.349302979221952</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.587646727894608</v>
+        <v>1.566192042382519</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1306706424999212</v>
+        <v>0.1307390665162854</v>
       </c>
       <c r="C76">
-        <v>4.150783650496663</v>
+        <v>3.934132690867248</v>
       </c>
       <c r="D76">
-        <v>13.46998365049666</v>
+        <v>13.45913269086725</v>
       </c>
       <c r="E76">
-        <v>4.529199999999999</v>
+        <v>4.734999999999999</v>
       </c>
       <c r="F76">
-        <v>15.2292</v>
+        <v>15.435</v>
       </c>
       <c r="G76">
         <v>5.91</v>
@@ -7519,28 +7519,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M76">
-        <v>1.370628</v>
+        <v>1.38915</v>
       </c>
       <c r="N76">
-        <v>0.7760386666666668</v>
+        <v>0.7575166666666666</v>
       </c>
       <c r="O76">
-        <v>0.1707285066666667</v>
+        <v>0.1666536666666666</v>
       </c>
       <c r="P76">
-        <v>0.60531016</v>
+        <v>0.5908629999999999</v>
       </c>
       <c r="Q76">
-        <v>2.00531016</v>
+        <v>1.990863</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.302779394230466</v>
+        <v>0.3123562660651418</v>
       </c>
       <c r="T76">
-        <v>3.349302979221952</v>
+        <v>3.47412172378923</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.566192042382519</v>
+        <v>1.545309481817418</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1307390665162854</v>
+        <v>0.1308074905326497</v>
       </c>
       <c r="C77">
-        <v>3.934132690867248</v>
+        <v>3.71749919949233</v>
       </c>
       <c r="D77">
-        <v>13.45913269086725</v>
+        <v>13.44829919949233</v>
       </c>
       <c r="E77">
-        <v>4.734999999999999</v>
+        <v>4.940799999999999</v>
       </c>
       <c r="F77">
-        <v>15.435</v>
+        <v>15.6408</v>
       </c>
       <c r="G77">
         <v>5.91</v>
@@ -7601,28 +7601,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M77">
-        <v>1.38915</v>
+        <v>1.407672</v>
       </c>
       <c r="N77">
-        <v>0.7575166666666666</v>
+        <v>0.7389946666666667</v>
       </c>
       <c r="O77">
-        <v>0.1666536666666666</v>
+        <v>0.1625788266666667</v>
       </c>
       <c r="P77">
-        <v>0.5908629999999999</v>
+        <v>0.57641584</v>
       </c>
       <c r="Q77">
-        <v>1.990863</v>
+        <v>1.97641584</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3123562660651418</v>
+        <v>0.3227312105527072</v>
       </c>
       <c r="T77">
-        <v>3.47412172378923</v>
+        <v>3.609342030403781</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.545309481817418</v>
+        <v>1.524976462319821</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1308074905326497</v>
+        <v>0.130875914549014</v>
       </c>
       <c r="C78">
-        <v>3.71749919949233</v>
+        <v>3.500883134224324</v>
       </c>
       <c r="D78">
-        <v>13.44829919949233</v>
+        <v>13.43748313422432</v>
       </c>
       <c r="E78">
-        <v>4.940799999999999</v>
+        <v>5.146599999999999</v>
       </c>
       <c r="F78">
-        <v>15.6408</v>
+        <v>15.8466</v>
       </c>
       <c r="G78">
         <v>5.91</v>
@@ -7683,28 +7683,28 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M78">
-        <v>1.407672</v>
+        <v>1.426194</v>
       </c>
       <c r="N78">
-        <v>0.7389946666666667</v>
+        <v>0.7204726666666668</v>
       </c>
       <c r="O78">
-        <v>0.1625788266666667</v>
+        <v>0.1585039866666667</v>
       </c>
       <c r="P78">
-        <v>0.57641584</v>
+        <v>0.5619686800000001</v>
       </c>
       <c r="Q78">
-        <v>1.97641584</v>
+        <v>1.96196868</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3227312105527072</v>
+        <v>0.3340083241261478</v>
       </c>
       <c r="T78">
-        <v>3.609342030403781</v>
+        <v>3.756320624550032</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.524976462319821</v>
+        <v>1.505171573198784</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.130875914549014</v>
+        <v>0.1689639098247867</v>
       </c>
       <c r="C79">
-        <v>3.500883134224324</v>
+        <v>-0.8604101012754999</v>
       </c>
       <c r="D79">
-        <v>13.43748313422432</v>
+        <v>9.281989898724499</v>
       </c>
       <c r="E79">
-        <v>5.146599999999999</v>
+        <v>5.352399999999999</v>
       </c>
       <c r="F79">
-        <v>15.8466</v>
+        <v>16.0524</v>
       </c>
       <c r="G79">
         <v>5.91</v>
@@ -7765,45 +7765,45 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M79">
-        <v>1.426194</v>
+        <v>2.35649232</v>
       </c>
       <c r="N79">
-        <v>0.7204726666666668</v>
+        <v>-0.2098256533333336</v>
       </c>
       <c r="O79">
-        <v>0.1585039866666667</v>
+        <v>-0.04616164373333339</v>
       </c>
       <c r="P79">
-        <v>0.5619686800000001</v>
+        <v>-0.1636640096000002</v>
       </c>
       <c r="Q79">
-        <v>1.96196868</v>
+        <v>1.2363359904</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3340083241261478</v>
+        <v>0.3518534346807971</v>
       </c>
       <c r="T79">
-        <v>3.756320624550032</v>
+        <v>3.988902237267312</v>
       </c>
       <c r="U79">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.22</v>
+        <v>0.2004108660395153</v>
       </c>
       <c r="W79">
-        <v>0.0702</v>
+        <v>0.1173796848653992</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.505171573198784</v>
+        <v>0.9109584819977968</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1689639098247867</v>
+        <v>0.1699739098247867</v>
       </c>
       <c r="C80">
-        <v>-0.8604101012754999</v>
+        <v>-1.141707521071172</v>
       </c>
       <c r="D80">
-        <v>9.281989898724499</v>
+        <v>9.206492478928826</v>
       </c>
       <c r="E80">
-        <v>5.352399999999999</v>
+        <v>5.558199999999999</v>
       </c>
       <c r="F80">
-        <v>16.0524</v>
+        <v>16.2582</v>
       </c>
       <c r="G80">
         <v>5.91</v>
@@ -7847,37 +7847,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M80">
-        <v>2.35649232</v>
+        <v>2.38670376</v>
       </c>
       <c r="N80">
-        <v>-0.2098256533333336</v>
+        <v>-0.2400370933333336</v>
       </c>
       <c r="O80">
-        <v>-0.04616164373333339</v>
+        <v>-0.05280816053333338</v>
       </c>
       <c r="P80">
-        <v>-0.1636640096000002</v>
+        <v>-0.1872289328000002</v>
       </c>
       <c r="Q80">
-        <v>1.2363359904</v>
+        <v>1.2127710672</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3518534346807971</v>
+        <v>0.366427407760835</v>
       </c>
       <c r="T80">
-        <v>3.988902237267312</v>
+        <v>4.17884996285147</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2004108660395153</v>
+        <v>0.1978740196339518</v>
       </c>
       <c r="W80">
-        <v>0.1173796848653992</v>
+        <v>0.1177520939177359</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.9109584819977968</v>
+        <v>0.8994273619725083</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1699739098247867</v>
+        <v>0.1709839098247867</v>
       </c>
       <c r="C81">
-        <v>-1.141707521071172</v>
+        <v>-1.421786694942101</v>
       </c>
       <c r="D81">
-        <v>9.206492478928826</v>
+        <v>9.132213305057897</v>
       </c>
       <c r="E81">
-        <v>5.558199999999999</v>
+        <v>5.763999999999999</v>
       </c>
       <c r="F81">
-        <v>16.2582</v>
+        <v>16.464</v>
       </c>
       <c r="G81">
         <v>5.91</v>
@@ -7929,37 +7929,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M81">
-        <v>2.38670376</v>
+        <v>2.4169152</v>
       </c>
       <c r="N81">
-        <v>-0.2400370933333336</v>
+        <v>-0.2702485333333335</v>
       </c>
       <c r="O81">
-        <v>-0.05280816053333338</v>
+        <v>-0.05945467733333338</v>
       </c>
       <c r="P81">
-        <v>-0.1872289328000002</v>
+        <v>-0.2107938560000002</v>
       </c>
       <c r="Q81">
-        <v>1.2127710672</v>
+        <v>1.189206144</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.366427407760835</v>
+        <v>0.3824587781488769</v>
       </c>
       <c r="T81">
-        <v>4.17884996285147</v>
+        <v>4.387792460994045</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1978740196339518</v>
+        <v>0.1954005943885274</v>
       </c>
       <c r="W81">
-        <v>0.1177520939177359</v>
+        <v>0.1181151927437642</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8994273619725083</v>
+        <v>0.8881845199478519</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1709839098247867</v>
+        <v>0.1719939098247867</v>
       </c>
       <c r="C82">
-        <v>-1.421786694942101</v>
+        <v>-1.70067687378603</v>
       </c>
       <c r="D82">
-        <v>9.132213305057897</v>
+        <v>9.059123126213969</v>
       </c>
       <c r="E82">
-        <v>5.763999999999999</v>
+        <v>5.969799999999999</v>
       </c>
       <c r="F82">
-        <v>16.464</v>
+        <v>16.6698</v>
       </c>
       <c r="G82">
         <v>5.91</v>
@@ -8011,37 +8011,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M82">
-        <v>2.4169152</v>
+        <v>2.44712664</v>
       </c>
       <c r="N82">
-        <v>-0.2702485333333335</v>
+        <v>-0.3004599733333335</v>
       </c>
       <c r="O82">
-        <v>-0.05945467733333338</v>
+        <v>-0.06610119413333337</v>
       </c>
       <c r="P82">
-        <v>-0.2107938560000002</v>
+        <v>-0.2343587792000001</v>
       </c>
       <c r="Q82">
-        <v>1.189206144</v>
+        <v>1.1656412208</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3824587781488769</v>
+        <v>0.4001776612093439</v>
       </c>
       <c r="T82">
-        <v>4.387792460994045</v>
+        <v>4.61872890630952</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1954005943885274</v>
+        <v>0.1929882413713851</v>
       </c>
       <c r="W82">
-        <v>0.1181151927437642</v>
+        <v>0.1184693261666807</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8881845199478519</v>
+        <v>0.8772192789608414</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1719939098247867</v>
+        <v>0.1730039098247867</v>
       </c>
       <c r="C83">
-        <v>-1.70067687378603</v>
+        <v>-1.978406379491313</v>
       </c>
       <c r="D83">
-        <v>9.059123126213969</v>
+        <v>8.987193620508686</v>
       </c>
       <c r="E83">
-        <v>5.969799999999999</v>
+        <v>6.175599999999999</v>
       </c>
       <c r="F83">
-        <v>16.6698</v>
+        <v>16.8756</v>
       </c>
       <c r="G83">
         <v>5.91</v>
@@ -8093,37 +8093,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M83">
-        <v>2.44712664</v>
+        <v>2.47733808</v>
       </c>
       <c r="N83">
-        <v>-0.3004599733333335</v>
+        <v>-0.3306714133333335</v>
       </c>
       <c r="O83">
-        <v>-0.06610119413333337</v>
+        <v>-0.07274771093333338</v>
       </c>
       <c r="P83">
-        <v>-0.2343587792000001</v>
+        <v>-0.2579237024000001</v>
       </c>
       <c r="Q83">
-        <v>1.1656412208</v>
+        <v>1.1420762976</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4001776612093439</v>
+        <v>0.4198653090543075</v>
       </c>
       <c r="T83">
-        <v>4.61872890630952</v>
+        <v>4.875324956660049</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1929882413713851</v>
+        <v>0.1906347262327097</v>
       </c>
       <c r="W83">
-        <v>0.1184693261666807</v>
+        <v>0.1188148221890382</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8772192789608414</v>
+        <v>0.8665214828759531</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1730039098247867</v>
+        <v>0.1740139098247867</v>
       </c>
       <c r="C84">
-        <v>-1.978406379491313</v>
+        <v>-2.25500264152808</v>
       </c>
       <c r="D84">
-        <v>8.987193620508686</v>
+        <v>8.916397358471919</v>
       </c>
       <c r="E84">
-        <v>6.175599999999999</v>
+        <v>6.381399999999999</v>
       </c>
       <c r="F84">
-        <v>16.8756</v>
+        <v>17.0814</v>
       </c>
       <c r="G84">
         <v>5.91</v>
@@ -8175,37 +8175,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M84">
-        <v>2.47733808</v>
+        <v>2.50754952</v>
       </c>
       <c r="N84">
-        <v>-0.3306714133333335</v>
+        <v>-0.3608828533333335</v>
       </c>
       <c r="O84">
-        <v>-0.07274771093333338</v>
+        <v>-0.07939422773333336</v>
       </c>
       <c r="P84">
-        <v>-0.2579237024000001</v>
+        <v>-0.2814886256000001</v>
       </c>
       <c r="Q84">
-        <v>1.1420762976</v>
+        <v>1.1185113744</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4198653090543075</v>
+        <v>0.4418691507633846</v>
       </c>
       <c r="T84">
-        <v>4.875324956660049</v>
+        <v>5.162108777640054</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1906347262327097</v>
+        <v>0.1883379223021951</v>
       </c>
       <c r="W84">
-        <v>0.1188148221890382</v>
+        <v>0.1191519930060378</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8665214828759531</v>
+        <v>0.8560814650099777</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1740139098247867</v>
+        <v>0.1750239098247867</v>
       </c>
       <c r="C85">
-        <v>-2.25500264152808</v>
+        <v>-2.530492231823459</v>
       </c>
       <c r="D85">
-        <v>8.916397358471919</v>
+        <v>8.84670776817654</v>
       </c>
       <c r="E85">
-        <v>6.381399999999999</v>
+        <v>6.587199999999999</v>
       </c>
       <c r="F85">
-        <v>17.0814</v>
+        <v>17.2872</v>
       </c>
       <c r="G85">
         <v>5.91</v>
@@ -8257,37 +8257,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M85">
-        <v>2.50754952</v>
+        <v>2.53776096</v>
       </c>
       <c r="N85">
-        <v>-0.3608828533333335</v>
+        <v>-0.3910942933333335</v>
       </c>
       <c r="O85">
-        <v>-0.07939422773333336</v>
+        <v>-0.08604074453333337</v>
       </c>
       <c r="P85">
-        <v>-0.2814886256000001</v>
+        <v>-0.3050535488000001</v>
       </c>
       <c r="Q85">
-        <v>1.1185113744</v>
+        <v>1.0949464512</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4418691507633846</v>
+        <v>0.4666234726860961</v>
       </c>
       <c r="T85">
-        <v>5.162108777640054</v>
+        <v>5.484740576242557</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1883379223021951</v>
+        <v>0.1860958041795499</v>
       </c>
       <c r="W85">
-        <v>0.1191519930060378</v>
+        <v>0.1194811359464421</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8560814650099777</v>
+        <v>0.8458900189979542</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1750239098247867</v>
+        <v>0.1760339098247867</v>
       </c>
       <c r="C86">
-        <v>-2.530492231823457</v>
+        <v>-2.804900898014003</v>
       </c>
       <c r="D86">
-        <v>8.846707768176541</v>
+        <v>8.778099101985996</v>
       </c>
       <c r="E86">
-        <v>6.587199999999999</v>
+        <v>6.792999999999999</v>
       </c>
       <c r="F86">
-        <v>17.2872</v>
+        <v>17.493</v>
       </c>
       <c r="G86">
         <v>5.91</v>
@@ -8339,37 +8339,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M86">
-        <v>2.53776096</v>
+        <v>2.5679724</v>
       </c>
       <c r="N86">
-        <v>-0.3910942933333335</v>
+        <v>-0.4213057333333334</v>
       </c>
       <c r="O86">
-        <v>-0.08604074453333337</v>
+        <v>-0.09268726133333335</v>
       </c>
       <c r="P86">
-        <v>-0.3050535488000001</v>
+        <v>-0.3286184720000001</v>
       </c>
       <c r="Q86">
-        <v>1.0949464512</v>
+        <v>1.071381528</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4666234726860958</v>
+        <v>0.4946783708651689</v>
       </c>
       <c r="T86">
-        <v>5.484740576242553</v>
+        <v>5.850389947992056</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1860958041795499</v>
+        <v>0.1839064417774376</v>
       </c>
       <c r="W86">
-        <v>0.1194811359464421</v>
+        <v>0.1198025343470722</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8458900189979542</v>
+        <v>0.8359383717156254</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1760339098247867</v>
+        <v>0.1770439098247867</v>
       </c>
       <c r="C87">
-        <v>-2.804900898014003</v>
+        <v>-3.078253595162709</v>
       </c>
       <c r="D87">
-        <v>8.778099101985996</v>
+        <v>8.71054640483729</v>
       </c>
       <c r="E87">
-        <v>6.792999999999999</v>
+        <v>6.998799999999999</v>
       </c>
       <c r="F87">
-        <v>17.493</v>
+        <v>17.6988</v>
       </c>
       <c r="G87">
         <v>5.91</v>
@@ -8421,37 +8421,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M87">
-        <v>2.5679724</v>
+        <v>2.59818384</v>
       </c>
       <c r="N87">
-        <v>-0.4213057333333334</v>
+        <v>-0.4515171733333334</v>
       </c>
       <c r="O87">
-        <v>-0.09268726133333335</v>
+        <v>-0.09933377813333336</v>
       </c>
       <c r="P87">
-        <v>-0.3286184720000001</v>
+        <v>-0.3521833952000001</v>
       </c>
       <c r="Q87">
-        <v>1.071381528</v>
+        <v>1.0478166048</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4946783708651689</v>
+        <v>0.5267411116412525</v>
       </c>
       <c r="T87">
-        <v>5.850389947992056</v>
+        <v>6.268274944277205</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1839064417774376</v>
+        <v>0.1817679947800255</v>
       </c>
       <c r="W87">
-        <v>0.1198025343470722</v>
+        <v>0.1201164583662923</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8359383717156254</v>
+        <v>0.8262181580910251</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1770439098247867</v>
+        <v>0.1780539098247867</v>
       </c>
       <c r="C88">
-        <v>-3.078253595162709</v>
+        <v>-3.350574516022752</v>
       </c>
       <c r="D88">
-        <v>8.71054640483729</v>
+        <v>8.644025483977247</v>
       </c>
       <c r="E88">
-        <v>6.998799999999999</v>
+        <v>7.204599999999999</v>
       </c>
       <c r="F88">
-        <v>17.6988</v>
+        <v>17.9046</v>
       </c>
       <c r="G88">
         <v>5.91</v>
@@ -8503,37 +8503,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M88">
-        <v>2.59818384</v>
+        <v>2.62839528</v>
       </c>
       <c r="N88">
-        <v>-0.4515171733333334</v>
+        <v>-0.4817286133333334</v>
       </c>
       <c r="O88">
-        <v>-0.09933377813333336</v>
+        <v>-0.1059802949333333</v>
       </c>
       <c r="P88">
-        <v>-0.3521833952000001</v>
+        <v>-0.3757483184000001</v>
       </c>
       <c r="Q88">
-        <v>1.0478166048</v>
+        <v>1.0242516816</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5267411116412525</v>
+        <v>0.5637365817675025</v>
       </c>
       <c r="T88">
-        <v>6.268274944277205</v>
+        <v>6.750449939990835</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1817679947800255</v>
+        <v>0.1796787074837034</v>
       </c>
       <c r="W88">
-        <v>0.1201164583662923</v>
+        <v>0.1204231657413923</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8262181580910251</v>
+        <v>0.8167213976531972</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1780539098247867</v>
+        <v>0.1790639098247866</v>
       </c>
       <c r="C89">
-        <v>-3.350574516022752</v>
+        <v>-3.621887119925002</v>
       </c>
       <c r="D89">
-        <v>8.644025483977247</v>
+        <v>8.578512880074996</v>
       </c>
       <c r="E89">
-        <v>7.204599999999999</v>
+        <v>7.410399999999999</v>
       </c>
       <c r="F89">
-        <v>17.9046</v>
+        <v>18.1104</v>
       </c>
       <c r="G89">
         <v>5.91</v>
@@ -8585,37 +8585,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M89">
-        <v>2.62839528</v>
+        <v>2.65860672</v>
       </c>
       <c r="N89">
-        <v>-0.4817286133333334</v>
+        <v>-0.5119400533333334</v>
       </c>
       <c r="O89">
-        <v>-0.1059802949333333</v>
+        <v>-0.1126268117333333</v>
       </c>
       <c r="P89">
-        <v>-0.3757483184000001</v>
+        <v>-0.3993132416</v>
       </c>
       <c r="Q89">
-        <v>1.0242516816</v>
+        <v>1.0006867584</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5637365817675025</v>
+        <v>0.6068979635814611</v>
       </c>
       <c r="T89">
-        <v>6.750449939990835</v>
+        <v>7.312987434990072</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1796787074837034</v>
+        <v>0.1776369039895704</v>
       </c>
       <c r="W89">
-        <v>0.1204231657413923</v>
+        <v>0.1207229024943311</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8167213976531972</v>
+        <v>0.8074404726798654</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1790639098247866</v>
+        <v>0.2314888775618196</v>
       </c>
       <c r="C90">
-        <v>-3.621887119925002</v>
+        <v>-6.249632186720561</v>
       </c>
       <c r="D90">
-        <v>8.578512880074996</v>
+        <v>6.156567813279437</v>
       </c>
       <c r="E90">
-        <v>7.410399999999999</v>
+        <v>7.616199999999999</v>
       </c>
       <c r="F90">
-        <v>18.1104</v>
+        <v>18.3162</v>
       </c>
       <c r="G90">
         <v>5.91</v>
@@ -8667,45 +8667,45 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M90">
-        <v>2.65860672</v>
+        <v>3.67789296</v>
       </c>
       <c r="N90">
-        <v>-0.5119400533333334</v>
+        <v>-1.531226293333333</v>
       </c>
       <c r="O90">
-        <v>-0.1126268117333333</v>
+        <v>-0.3368697845333333</v>
       </c>
       <c r="P90">
-        <v>-0.3993132416</v>
+        <v>-1.1943565088</v>
       </c>
       <c r="Q90">
-        <v>1.0006867584</v>
+        <v>0.2056434912</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6068979635814611</v>
+        <v>0.6884065760618937</v>
       </c>
       <c r="T90">
-        <v>7.312987434990072</v>
+        <v>8.375317897050891</v>
       </c>
       <c r="U90">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1776369039895704</v>
+        <v>0.1284068546319702</v>
       </c>
       <c r="W90">
-        <v>0.1207229024943311</v>
+        <v>0.1750159035899004</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.8074404726798654</v>
+        <v>0.58366752105441</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2314888775618196</v>
+        <v>0.2330388775618197</v>
       </c>
       <c r="C91">
-        <v>-6.249632186720561</v>
+        <v>-6.506397457581219</v>
       </c>
       <c r="D91">
-        <v>6.156567813279437</v>
+        <v>6.10560254241878</v>
       </c>
       <c r="E91">
-        <v>7.616199999999999</v>
+        <v>7.821999999999999</v>
       </c>
       <c r="F91">
-        <v>18.3162</v>
+        <v>18.522</v>
       </c>
       <c r="G91">
         <v>5.91</v>
@@ -8749,37 +8749,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M91">
-        <v>3.67789296</v>
+        <v>3.7192176</v>
       </c>
       <c r="N91">
-        <v>-1.531226293333333</v>
+        <v>-1.572550933333333</v>
       </c>
       <c r="O91">
-        <v>-0.3368697845333333</v>
+        <v>-0.3459612053333334</v>
       </c>
       <c r="P91">
-        <v>-1.1943565088</v>
+        <v>-1.226589728</v>
       </c>
       <c r="Q91">
-        <v>0.2056434912</v>
+        <v>0.1734102720000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6884065760618937</v>
+        <v>0.7526672336680832</v>
       </c>
       <c r="T91">
-        <v>8.375317897050891</v>
+        <v>9.212849686755982</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1284068546319702</v>
+        <v>0.1269801118027261</v>
       </c>
       <c r="W91">
-        <v>0.1750159035899004</v>
+        <v>0.1753023935500126</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.58366752105441</v>
+        <v>0.5771823263760277</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2330388775618197</v>
+        <v>0.2345888775618196</v>
       </c>
       <c r="C92">
-        <v>-6.506397457581219</v>
+        <v>-6.762325855307665</v>
       </c>
       <c r="D92">
-        <v>6.10560254241878</v>
+        <v>6.055474144692332</v>
       </c>
       <c r="E92">
-        <v>7.821999999999999</v>
+        <v>8.027799999999999</v>
       </c>
       <c r="F92">
-        <v>18.522</v>
+        <v>18.7278</v>
       </c>
       <c r="G92">
         <v>5.91</v>
@@ -8831,37 +8831,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M92">
-        <v>3.7192176</v>
+        <v>3.76054224</v>
       </c>
       <c r="N92">
-        <v>-1.572550933333333</v>
+        <v>-1.613875573333333</v>
       </c>
       <c r="O92">
-        <v>-0.3459612053333334</v>
+        <v>-0.3550526261333334</v>
       </c>
       <c r="P92">
-        <v>-1.226589728</v>
+        <v>-1.2588229472</v>
       </c>
       <c r="Q92">
-        <v>0.1734102720000001</v>
+        <v>0.1411770528</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7526672336680832</v>
+        <v>0.8312080374089813</v>
       </c>
       <c r="T92">
-        <v>9.212849686755982</v>
+        <v>10.23649965195109</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1269801118027261</v>
+        <v>0.1255847259587401</v>
       </c>
       <c r="W92">
-        <v>0.1753023935500126</v>
+        <v>0.175582587027485</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5771823263760277</v>
+        <v>0.5708396634488186</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2345888775618196</v>
+        <v>0.2361388775618197</v>
       </c>
       <c r="C93">
-        <v>-6.762325855307665</v>
+        <v>-7.017437824803887</v>
       </c>
       <c r="D93">
-        <v>6.055474144692332</v>
+        <v>6.006162175196112</v>
       </c>
       <c r="E93">
-        <v>8.027799999999999</v>
+        <v>8.233599999999999</v>
       </c>
       <c r="F93">
-        <v>18.7278</v>
+        <v>18.9336</v>
       </c>
       <c r="G93">
         <v>5.91</v>
@@ -8913,37 +8913,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M93">
-        <v>3.76054224</v>
+        <v>3.80186688</v>
       </c>
       <c r="N93">
-        <v>-1.613875573333333</v>
+        <v>-1.655200213333333</v>
       </c>
       <c r="O93">
-        <v>-0.3550526261333334</v>
+        <v>-0.3641440469333334</v>
       </c>
       <c r="P93">
-        <v>-1.2588229472</v>
+        <v>-1.2910561664</v>
       </c>
       <c r="Q93">
-        <v>0.1411770528</v>
+        <v>0.1089438335999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8312080374089813</v>
+        <v>0.9293840420851044</v>
       </c>
       <c r="T93">
-        <v>10.23649965195109</v>
+        <v>11.51606210844498</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1255847259587401</v>
+        <v>0.1242196745896234</v>
       </c>
       <c r="W93">
-        <v>0.175582587027485</v>
+        <v>0.1758566893424036</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5708396634488186</v>
+        <v>0.564634884498288</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2361388775618197</v>
+        <v>0.2376888775618197</v>
       </c>
       <c r="C94">
-        <v>-7.017437824803887</v>
+        <v>-7.271753150391504</v>
       </c>
       <c r="D94">
-        <v>6.006162175196112</v>
+        <v>5.957646849608494</v>
       </c>
       <c r="E94">
-        <v>8.233599999999999</v>
+        <v>8.439399999999999</v>
       </c>
       <c r="F94">
-        <v>18.9336</v>
+        <v>19.1394</v>
       </c>
       <c r="G94">
         <v>5.91</v>
@@ -8995,37 +8995,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M94">
-        <v>3.80186688</v>
+        <v>3.84319152</v>
       </c>
       <c r="N94">
-        <v>-1.655200213333333</v>
+        <v>-1.696524853333333</v>
       </c>
       <c r="O94">
-        <v>-0.3641440469333334</v>
+        <v>-0.3732354677333334</v>
       </c>
       <c r="P94">
-        <v>-1.2910561664</v>
+        <v>-1.3232893856</v>
       </c>
       <c r="Q94">
-        <v>0.1089438335999999</v>
+        <v>0.07671061440000004</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9293840420851044</v>
+        <v>1.055610333811548</v>
       </c>
       <c r="T94">
-        <v>11.51606210844498</v>
+        <v>13.16121383822284</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1242196745896234</v>
+        <v>0.1228839791639285</v>
       </c>
       <c r="W94">
-        <v>0.1758566893424036</v>
+        <v>0.1761248969838832</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.564634884498288</v>
+        <v>0.5585635416542204</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2376888775618197</v>
+        <v>0.2392388775618197</v>
       </c>
       <c r="C95">
-        <v>-7.271753150391504</v>
+        <v>-7.525290982275592</v>
       </c>
       <c r="D95">
-        <v>5.957646849608494</v>
+        <v>5.909909017724406</v>
       </c>
       <c r="E95">
-        <v>8.439399999999999</v>
+        <v>8.645199999999999</v>
       </c>
       <c r="F95">
-        <v>19.1394</v>
+        <v>19.3452</v>
       </c>
       <c r="G95">
         <v>5.91</v>
@@ -9077,37 +9077,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M95">
-        <v>3.84319152</v>
+        <v>3.88451616</v>
       </c>
       <c r="N95">
-        <v>-1.696524853333333</v>
+        <v>-1.737849493333333</v>
       </c>
       <c r="O95">
-        <v>-0.3732354677333334</v>
+        <v>-0.3823268885333334</v>
       </c>
       <c r="P95">
-        <v>-1.3232893856</v>
+        <v>-1.3555226048</v>
       </c>
       <c r="Q95">
-        <v>0.07671061440000004</v>
+        <v>0.04447739519999994</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.055610333811548</v>
+        <v>1.223912056113473</v>
       </c>
       <c r="T95">
-        <v>13.16121383822284</v>
+        <v>15.35474947792665</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1228839791639285</v>
+        <v>0.1215767027898441</v>
       </c>
       <c r="W95">
-        <v>0.1761248969838832</v>
+        <v>0.1763873980797993</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5585635416542204</v>
+        <v>0.5526213763174733</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2392388775618197</v>
+        <v>0.2407888775618197</v>
       </c>
       <c r="C96">
-        <v>-7.525290982275592</v>
+        <v>-7.778069861748186</v>
       </c>
       <c r="D96">
-        <v>5.909909017724406</v>
+        <v>5.862930138251813</v>
       </c>
       <c r="E96">
-        <v>8.645199999999999</v>
+        <v>8.850999999999999</v>
       </c>
       <c r="F96">
-        <v>19.3452</v>
+        <v>19.551</v>
       </c>
       <c r="G96">
         <v>5.91</v>
@@ -9159,37 +9159,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M96">
-        <v>3.88451616</v>
+        <v>3.9258408</v>
       </c>
       <c r="N96">
-        <v>-1.737849493333333</v>
+        <v>-1.779174133333333</v>
       </c>
       <c r="O96">
-        <v>-0.3823268885333334</v>
+        <v>-0.3914183093333333</v>
       </c>
       <c r="P96">
-        <v>-1.3555226048</v>
+        <v>-1.387755824</v>
       </c>
       <c r="Q96">
-        <v>0.04447739519999994</v>
+        <v>0.01224417600000027</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.223912056113473</v>
+        <v>1.459534467336168</v>
       </c>
       <c r="T96">
-        <v>15.35474947792665</v>
+        <v>18.42569937351199</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1215767027898441</v>
+        <v>0.1202969480236353</v>
       </c>
       <c r="W96">
-        <v>0.1763873980797993</v>
+        <v>0.1766443728368541</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5526213763174733</v>
+        <v>0.5468043091983421</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2407888775618197</v>
+        <v>0.2423388775618197</v>
       </c>
       <c r="C97">
-        <v>-7.778069861748186</v>
+        <v>-8.030107745199169</v>
       </c>
       <c r="D97">
-        <v>5.862930138251813</v>
+        <v>5.816692254800829</v>
       </c>
       <c r="E97">
-        <v>8.850999999999999</v>
+        <v>9.056799999999999</v>
       </c>
       <c r="F97">
-        <v>19.551</v>
+        <v>19.7568</v>
       </c>
       <c r="G97">
         <v>5.91</v>
@@ -9241,37 +9241,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M97">
-        <v>3.9258408</v>
+        <v>3.96716544</v>
       </c>
       <c r="N97">
-        <v>-1.779174133333333</v>
+        <v>-1.820498773333333</v>
       </c>
       <c r="O97">
-        <v>-0.3914183093333333</v>
+        <v>-0.4005097301333333</v>
       </c>
       <c r="P97">
-        <v>-1.387755824</v>
+        <v>-1.4199890432</v>
       </c>
       <c r="Q97">
-        <v>0.01224417600000027</v>
+        <v>-0.01998904319999961</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.459534467336168</v>
+        <v>1.812968084170211</v>
       </c>
       <c r="T97">
-        <v>18.42569937351199</v>
+        <v>23.03212421688999</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1202969480236353</v>
+        <v>0.1190438548150557</v>
       </c>
       <c r="W97">
-        <v>0.1766443728368541</v>
+        <v>0.1768959939531368</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5468043091983421</v>
+        <v>0.541108430977526</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2423388775618197</v>
+        <v>0.2438888775618197</v>
       </c>
       <c r="C98">
-        <v>-8.030107745199167</v>
+        <v>-8.281422026999909</v>
       </c>
       <c r="D98">
-        <v>5.816692254800831</v>
+        <v>5.771177973000089</v>
       </c>
       <c r="E98">
-        <v>9.056799999999999</v>
+        <v>9.262599999999999</v>
       </c>
       <c r="F98">
-        <v>19.7568</v>
+        <v>19.9626</v>
       </c>
       <c r="G98">
         <v>5.91</v>
@@ -9323,37 +9323,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M98">
-        <v>3.96716544</v>
+        <v>4.00849008</v>
       </c>
       <c r="N98">
-        <v>-1.820498773333333</v>
+        <v>-1.861823413333333</v>
       </c>
       <c r="O98">
-        <v>-0.4005097301333333</v>
+        <v>-0.4096011509333333</v>
       </c>
       <c r="P98">
-        <v>-1.4199890432</v>
+        <v>-1.4522222624</v>
       </c>
       <c r="Q98">
-        <v>-0.01998904319999961</v>
+        <v>-0.05222226239999972</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.812968084170206</v>
+        <v>2.402024112226941</v>
       </c>
       <c r="T98">
-        <v>23.03212421688993</v>
+        <v>30.70949895585324</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1190438548150557</v>
+        <v>0.117816598579849</v>
       </c>
       <c r="W98">
-        <v>0.1768959939531368</v>
+        <v>0.1771424270051663</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.541108430977526</v>
+        <v>0.535529993544768</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2438888775618197</v>
+        <v>0.2454388775618196</v>
       </c>
       <c r="C99">
-        <v>-8.281422026999909</v>
+        <v>-8.532029561320874</v>
       </c>
       <c r="D99">
-        <v>5.771177973000089</v>
+        <v>5.726370438679124</v>
       </c>
       <c r="E99">
-        <v>9.262599999999999</v>
+        <v>9.468399999999999</v>
       </c>
       <c r="F99">
-        <v>19.9626</v>
+        <v>20.1684</v>
       </c>
       <c r="G99">
         <v>5.91</v>
@@ -9405,37 +9405,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M99">
-        <v>4.00849008</v>
+        <v>4.04981472</v>
       </c>
       <c r="N99">
-        <v>-1.861823413333333</v>
+        <v>-1.903148053333333</v>
       </c>
       <c r="O99">
-        <v>-0.4096011509333333</v>
+        <v>-0.4186925717333333</v>
       </c>
       <c r="P99">
-        <v>-1.4522222624</v>
+        <v>-1.4844554816</v>
       </c>
       <c r="Q99">
-        <v>-0.05222226239999972</v>
+        <v>-0.08445548159999983</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.402024112226941</v>
+        <v>3.580136168340412</v>
       </c>
       <c r="T99">
-        <v>30.70949895585324</v>
+        <v>46.06424843377986</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.117816598579849</v>
+        <v>0.1166143883902587</v>
       </c>
       <c r="W99">
-        <v>0.1771424270051663</v>
+        <v>0.1773838308112361</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.535529993544768</v>
+        <v>0.530065401773903</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2454388775618196</v>
+        <v>0.2469888775618196</v>
       </c>
       <c r="C100">
-        <v>-8.532029561320874</v>
+        <v>-8.78194668294071</v>
       </c>
       <c r="D100">
-        <v>5.726370438679124</v>
+        <v>5.682253317059289</v>
       </c>
       <c r="E100">
-        <v>9.468399999999999</v>
+        <v>9.674199999999999</v>
       </c>
       <c r="F100">
-        <v>20.1684</v>
+        <v>20.3742</v>
       </c>
       <c r="G100">
         <v>5.91</v>
@@ -9487,37 +9487,37 @@
         <v>2.146666666666667</v>
       </c>
       <c r="M100">
-        <v>4.04981472</v>
+        <v>4.09113936</v>
       </c>
       <c r="N100">
-        <v>-1.903148053333333</v>
+        <v>-1.944472693333333</v>
       </c>
       <c r="O100">
-        <v>-0.4186925717333333</v>
+        <v>-0.4277839925333333</v>
       </c>
       <c r="P100">
-        <v>-1.4844554816</v>
+        <v>-1.5166887008</v>
       </c>
       <c r="Q100">
-        <v>-0.08445548159999983</v>
+        <v>-0.1166887007999997</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.580136168340412</v>
+        <v>7.114472336680825</v>
       </c>
       <c r="T100">
-        <v>46.06424843377986</v>
+        <v>92.12849686755972</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1166143883902587</v>
+        <v>0.1154364652752056</v>
       </c>
       <c r="W100">
-        <v>0.1773838308112361</v>
+        <v>0.1776203577727387</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.530065401773903</v>
+        <v>0.5247112057963889</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2469888775618196</v>
-      </c>
-      <c r="C101">
-        <v>-8.78194668294071</v>
-      </c>
-      <c r="D101">
-        <v>5.682253317059289</v>
-      </c>
-      <c r="E101">
-        <v>9.674199999999999</v>
-      </c>
-      <c r="F101">
-        <v>20.3742</v>
-      </c>
-      <c r="G101">
-        <v>5.91</v>
-      </c>
-      <c r="H101">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.546666666666667</v>
-      </c>
-      <c r="K101">
-        <v>1.4</v>
-      </c>
-      <c r="L101">
-        <v>2.146666666666667</v>
-      </c>
-      <c r="M101">
-        <v>4.09113936</v>
-      </c>
-      <c r="N101">
-        <v>-1.944472693333333</v>
-      </c>
-      <c r="O101">
-        <v>-0.4277839925333333</v>
-      </c>
-      <c r="P101">
-        <v>-1.5166887008</v>
-      </c>
-      <c r="Q101">
-        <v>-0.1166887007999997</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.114472336680825</v>
-      </c>
-      <c r="T101">
-        <v>92.12849686755972</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1154364652752056</v>
-      </c>
-      <c r="W101">
-        <v>0.1776203577727387</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5247112057963889</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
